--- a/claude/05.10.2026 - BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO/BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO.xlsx
+++ b/claude/05.10.2026 - BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO/BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Fuentes y notas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base'!$A$4:$V$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base'!$A$4:$Y$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -168,14 +168,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,7 +276,7 @@
   <commentList>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>No existe registro público de presidentes de CEAL. Se eligen cada año y son en su mayoría menores de edad. Completar con lo que informe cada establecimiento (ver hoja Fuentes y notas).</t>
+        <t>Establecimientos públicos: nómina 2026 del SLEP Puerto Cordillera (38 casos). Particulares: no hay registro público; completar con lo que informe cada establecimiento. Datos de menores de edad: uso restringido (ver hoja Fuentes y notas).</t>
       </text>
     </comment>
   </commentList>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V167"/>
+  <dimension ref="A1:Y167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -589,14 +589,17 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -609,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corte: 05.10.2026. Universo: 154 establecimientos con RBD vigentes en el Directorio Oficial MINEDUC 2025 + 9 jardines VTF del SLEP Puerto Cordillera. Celdas amarillas: por completar.</t>
+          <t>Corte: 05.10.2026. Universo: 154 establecimientos con RBD vigentes en el Directorio Oficial MINEDUC 2025 + 9 jardines VTF del SLEP Puerto Cordillera. Gobiernos estudiantiles 2026 de la educación pública integrados según nómina del SLEP. Celdas amarillas: por completar.</t>
         </is>
       </c>
     </row>
@@ -691,35 +694,50 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
+          <t>Cargo (gobierno estudiantil)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Correo presidente/a CEAL</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Fuente CEAL</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
           <t>Sitio web</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Sostenedor</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>Fuente contacto</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Fuente aniversario</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -792,32 +810,47 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>-29.96714592</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>-71.32640076</v>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -884,30 +917,45 @@
           <t>Resolución exenta 10049 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q6" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="U6" s="7" t="n">
         <v>-29.96734</v>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="V6" s="7" t="n">
         <v>-71.33910400000001</v>
       </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr"/>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="X6" s="8" t="inlineStr"/>
+      <c r="Y6" s="8" t="inlineStr">
         <is>
           <t>Director según tabla SLEP; MIME registra a Eduardo Andrés Alfaro Espinoza: confirmar</t>
         </is>
@@ -978,34 +1026,49 @@
           <t>Resolución exenta 10046 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>-30.05068</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>-71.252403</v>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Noticias SLEP Puerto Cordillera (128 años, julio 2019)</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Director según tabla SLEP; MIME registra a Carla Francisca Álvarez Ibáñez: confirmar</t>
         </is>
@@ -1076,34 +1139,49 @@
           <t>Resolución exenta 10050 de fecha 01/01/2002</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="U8" s="7" t="n">
         <v>-29.953659</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="V8" s="7" t="n">
         <v>-71.34324599999999</v>
       </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="Y8" s="8" t="inlineStr">
         <is>
           <t>Asumió por concurso de Alta Dirección Pública (SLEP, noticia 04.05.2026); la tabla del SLEP aún muestra al director anterior</t>
         </is>
@@ -1174,38 +1252,53 @@
           <t>Resolución exenta 10034 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>www.arraucoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>-29.961269</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>-71.33828699999999</v>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera (177° aniversario, mayo 2019)</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>Según MIME; el director que figura en la tabla del SLEP (Carlos Videla) pasó al IAC Estado de Israel en mayo de 2026: confirmar si es titular o subrogante</t>
         </is>
@@ -1276,34 +1369,49 @@
           <t>Resolución exenta 10051 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q10" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>-29.98613</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>-71.361214</v>
       </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="Y10" s="8" t="inlineStr">
         <is>
           <t>Director según tabla SLEP; MIME registra a Sergio Eduardo Carrasset Godoy: confirmar</t>
         </is>
@@ -1374,34 +1482,49 @@
           <t>Resolución exenta 10067 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>-30.26317</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>-71.48988300000001</v>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="X11" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1468,34 +1591,49 @@
           <t>Resolución exenta 10038 de fecha 01/01/1981</t>
         </is>
       </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q12" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="U12" s="7" t="n">
         <v>-30.19949</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="V12" s="7" t="n">
         <v>-71.429733</v>
       </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr"/>
+      <c r="Y12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1562,34 +1700,49 @@
           <t>Resolución exenta 10059 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>-29.967279</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>-71.32762099999999</v>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="X13" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
+      <c r="Y13" s="5" t="inlineStr">
         <is>
           <t>Director según tabla SLEP; MIME registra a Patricia Milena Maya Podestá: confirmar</t>
         </is>
@@ -1660,34 +1813,49 @@
           <t>Resolución exenta 2263 de fecha 30/06/2005</t>
         </is>
       </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q14" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="U14" s="7" t="n">
         <v>-29.95595</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="V14" s="7" t="n">
         <v>-71.247238</v>
       </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
+      <c r="Y14" s="8" t="inlineStr">
         <is>
           <t>Asumió por concurso de Alta Dirección Pública (SLEP, noticia 04.05.2026); la tabla del SLEP aún muestra al director anterior</t>
         </is>
@@ -1758,34 +1926,49 @@
           <t>Resolución exenta 194 de fecha 29/03/1983</t>
         </is>
       </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Presidente de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>-29.954359</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>-71.33627300000001</v>
       </c>
-      <c r="T15" s="5" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="X15" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1854,32 +2037,47 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr"/>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="U16" s="7" t="n">
         <v>-29.96768951</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="V16" s="7" t="n">
         <v>-71.32416533999999</v>
       </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="X16" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr"/>
+      <c r="Y16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1946,34 +2144,49 @@
           <t>Resolución exenta 10033 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O17" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Presidente de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>-29.971701</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="V17" s="4" t="n">
         <v>-71.325447</v>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="W17" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="X17" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2040,38 +2253,53 @@
           <t>Resolución exenta 10058 de fecha 15/01/1981</t>
         </is>
       </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>www.joseagustinalfaro.net</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="U18" s="7" t="n">
         <v>-29.957069</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="V18" s="7" t="n">
         <v>-71.261627</v>
       </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="X18" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera (60 años, mayo 2025)</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr"/>
+      <c r="Y18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2138,34 +2366,49 @@
           <t>Resolución exenta 1502 de fecha 10/05/2005</t>
         </is>
       </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>-29.936899</v>
       </c>
-      <c r="S19" s="4" t="n">
+      <c r="V19" s="4" t="n">
         <v>-71.339867</v>
       </c>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="W19" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="X19" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2232,30 +2475,45 @@
           <t>Resolución exenta 10048 de fecha 02/01/1981</t>
         </is>
       </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="U20" s="7" t="n">
         <v>-29.97381</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="V20" s="7" t="n">
         <v>-71.299103</v>
       </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr"/>
-      <c r="V20" s="8" t="inlineStr"/>
+      <c r="X20" s="8" t="inlineStr"/>
+      <c r="Y20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2322,38 +2580,53 @@
           <t>Resolución exenta 773 de fecha 17/03/2005</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>https://sites.google.com/slepuertocordillera.cl/escuelapahccoquimbo/boletín-informativo-no</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>-29.951389</v>
       </c>
-      <c r="S21" s="4" t="n">
+      <c r="V21" s="4" t="n">
         <v>-71.349281</v>
       </c>
-      <c r="T21" s="5" t="inlineStr">
+      <c r="W21" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2420,38 +2693,53 @@
           <t>Resolución exenta 10035 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>www.eapinto.cl</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="U22" s="7" t="n">
         <v>-29.95573</v>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="V22" s="7" t="n">
         <v>-71.339958</v>
       </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="X22" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr"/>
+      <c r="Y22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2518,34 +2806,49 @@
           <t>Resolución exenta 1504 de fecha 10/05/2005</t>
         </is>
       </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>-29.98612</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="V23" s="4" t="n">
         <v>-71.332314</v>
       </c>
-      <c r="T23" s="5" t="inlineStr">
+      <c r="W23" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="X23" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V23" s="5" t="inlineStr">
+      <c r="Y23" s="5" t="inlineStr">
         <is>
           <t>Director según tabla SLEP; MIME registra a Ricardo Antonio Ubilla Astudillo: confirmar</t>
         </is>
@@ -2616,38 +2919,53 @@
           <t>Resolución exenta 00184 de fecha 28/03/1989</t>
         </is>
       </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>www.escuelasanrafaelcoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="U24" s="7" t="n">
         <v>-30.01071</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="V24" s="7" t="n">
         <v>-71.256767</v>
       </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="X24" s="8" t="inlineStr">
         <is>
           <t>Noticias SLEP Puerto Cordillera (68° aniversario, abril 2019)</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr"/>
+      <c r="Y24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -2714,34 +3032,49 @@
           <t>Resolución exenta 10053 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>-29.962</v>
       </c>
-      <c r="S25" s="4" t="n">
+      <c r="V25" s="4" t="n">
         <v>-71.254204</v>
       </c>
-      <c r="T25" s="5" t="inlineStr">
+      <c r="W25" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="X25" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2808,38 +3141,53 @@
           <t>Resolución exenta 29 de fecha 07/01/1991</t>
         </is>
       </c>
-      <c r="O26" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta del gobierno escolar</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>sites.google.com/view/escuela-deportiva-digital/</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="U26" s="7" t="n">
         <v>-29.96139</v>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="V26" s="7" t="n">
         <v>-71.348793</v>
       </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="X26" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr"/>
+      <c r="Y26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2867,7 +3215,7 @@
       <c r="G27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -2887,12 +3235,12 @@
           <t>Camarones Km. 416 -ruta 5</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M27" s="13" t="inlineStr">
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -2907,25 +3255,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>-30.436291</v>
       </c>
-      <c r="S27" s="4" t="n">
+      <c r="V27" s="4" t="n">
         <v>-71.37904399999999</v>
       </c>
-      <c r="T27" s="5" t="inlineStr">
+      <c r="W27" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar; Sin matrícula 2025 y fuera del listado del SLEP: probable receso; Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -2996,34 +3347,49 @@
           <t>Resolución exenta 10041 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q28" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="U28" s="7" t="n">
         <v>-29.97542</v>
       </c>
-      <c r="S28" s="7" t="n">
+      <c r="V28" s="7" t="n">
         <v>-71.219368</v>
       </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="X28" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
+      <c r="Y28" s="8" t="inlineStr">
         <is>
           <t>Teléfono tomado de MIME (el SLEP no publica uno); Docente encargada desde marzo de 2025 (SLEP, noticia 06.03.2025) y según MIME; la tabla del SLEP muestra al encargado anterior</t>
         </is>
@@ -3094,34 +3460,49 @@
           <t>Resolución exenta 10054 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O29" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>-29.95158</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>-71.296204</v>
       </c>
-      <c r="T29" s="5" t="inlineStr">
+      <c r="W29" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U29" s="5" t="inlineStr">
+      <c r="X29" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3188,34 +3569,49 @@
           <t>Resolución exenta 10065 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="U30" s="7" t="n">
         <v>-30.29287</v>
       </c>
-      <c r="S30" s="7" t="n">
+      <c r="V30" s="7" t="n">
         <v>-71.609261</v>
       </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="X30" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr"/>
+      <c r="Y30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -3282,34 +3678,49 @@
           <t>Resolución exenta 1918 de fecha 21/12/1982</t>
         </is>
       </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>-30.197321</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="V31" s="4" t="n">
         <v>-71.223686</v>
       </c>
-      <c r="T31" s="5" t="inlineStr">
+      <c r="W31" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U31" s="5" t="inlineStr">
+      <c r="X31" s="5" t="inlineStr">
         <is>
           <t>Noticias SLEP Puerto Cordillera (145 años, nov. 2025); el PEI indica 1900</t>
         </is>
       </c>
-      <c r="V31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3376,34 +3787,49 @@
           <t>Resolución exenta 10043 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O32" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr"/>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="U32" s="7" t="n">
         <v>-30.064871</v>
       </c>
-      <c r="S32" s="7" t="n">
+      <c r="V32" s="7" t="n">
         <v>-71.36621100000001</v>
       </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="X32" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
+      <c r="Y32" s="8" t="inlineStr">
         <is>
           <t>Teléfono tomado de MIME (el SLEP no publica uno)</t>
         </is>
@@ -3459,7 +3885,7 @@
           <t>Camino Coquimbo O’Higgins s/n</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -3474,34 +3900,49 @@
           <t>Resolución exenta 10063 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O33" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>-30.138849</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>-71.215828</v>
       </c>
-      <c r="T33" s="5" t="inlineStr">
+      <c r="W33" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U33" s="5" t="inlineStr">
+      <c r="X33" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V33" s="5" t="inlineStr"/>
+      <c r="Y33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3568,34 +4009,49 @@
           <t>Resolución exenta 10066 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O34" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr"/>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr"/>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R34" s="7" t="n">
+      <c r="U34" s="7" t="n">
         <v>-30.34646</v>
       </c>
-      <c r="S34" s="7" t="n">
+      <c r="V34" s="7" t="n">
         <v>-71.558617</v>
       </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
+      <c r="Y34" s="8" t="inlineStr">
         <is>
           <t>Teléfono tomado de MIME (el SLEP no publica uno)</t>
         </is>
@@ -3666,34 +4122,49 @@
           <t>Resolución exenta 10060 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O35" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>-30.213289</v>
       </c>
-      <c r="S35" s="4" t="n">
+      <c r="V35" s="4" t="n">
         <v>-71.257874</v>
       </c>
-      <c r="T35" s="5" t="inlineStr">
+      <c r="W35" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U35" s="5" t="inlineStr">
+      <c r="X35" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V35" s="5" t="inlineStr"/>
+      <c r="Y35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3760,34 +4231,49 @@
           <t>Resolución exenta 10062 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P36" s="7" t="inlineStr"/>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q36" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr"/>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R36" s="7" t="n">
+      <c r="U36" s="7" t="n">
         <v>-30.27844</v>
       </c>
-      <c r="S36" s="7" t="n">
+      <c r="V36" s="7" t="n">
         <v>-71.25250200000001</v>
       </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC) (fecha que asume la comunidad)</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
+      <c r="Y36" s="8" t="inlineStr">
         <is>
           <t>Teléfono tomado de MIME (el SLEP no publica uno)</t>
         </is>
@@ -3858,34 +4344,49 @@
           <t>Resolución exenta 1452 de fecha 06/05/2005</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>-29.970631</v>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="V37" s="4" t="n">
         <v>-71.325447</v>
       </c>
-      <c r="T37" s="5" t="inlineStr">
+      <c r="W37" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U37" s="5" t="inlineStr">
+      <c r="X37" s="5" t="inlineStr">
         <is>
           <t>Noticias SLEP Puerto Cordillera (14 años, mayo 2019)</t>
         </is>
       </c>
-      <c r="V37" s="5" t="inlineStr">
+      <c r="Y37" s="5" t="inlineStr">
         <is>
           <t>Asumió por concurso de Alta Dirección Pública (SLEP, noticia 04.05.2026); la tabla del SLEP aún muestra al director anterior</t>
         </is>
@@ -3956,34 +4457,49 @@
           <t>Resolución exenta 1451 de fecha 06/05/2005</t>
         </is>
       </c>
-      <c r="O38" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr"/>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr"/>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R38" s="7" t="n">
+      <c r="U38" s="7" t="n">
         <v>-29.990379</v>
       </c>
-      <c r="S38" s="7" t="n">
+      <c r="V38" s="7" t="n">
         <v>-71.331596</v>
       </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="W38" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="X38" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V38" s="8" t="inlineStr"/>
+      <c r="Y38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4050,38 +4566,53 @@
           <t>Resolución exenta 339 de fecha 01/03/2018</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
         <is>
           <t>www.isccoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>-29.96055</v>
       </c>
-      <c r="S39" s="4" t="n">
+      <c r="V39" s="4" t="n">
         <v>-71.34013400000001</v>
       </c>
-      <c r="T39" s="5" t="inlineStr">
+      <c r="W39" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U39" s="5" t="inlineStr">
+      <c r="X39" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera (120 años, mayo 2025)</t>
         </is>
       </c>
-      <c r="V39" s="5" t="inlineStr"/>
+      <c r="Y39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -4148,34 +4679,49 @@
           <t>Resolución exenta 1765 de fecha 02/08/2000</t>
         </is>
       </c>
-      <c r="O40" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr"/>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R40" s="7" t="n">
+      <c r="U40" s="7" t="n">
         <v>-30.26264</v>
       </c>
-      <c r="S40" s="7" t="n">
+      <c r="V40" s="7" t="n">
         <v>-71.49340100000001</v>
       </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="W40" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="X40" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr"/>
+      <c r="Y40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4242,34 +4788,49 @@
           <t>Resolución exenta 10070 de fecha 15/12/1981</t>
         </is>
       </c>
-      <c r="O41" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>Presidenta de gobierno estudiantil</t>
+        </is>
+      </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr"/>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>-29.95303</v>
       </c>
-      <c r="S41" s="4" t="n">
+      <c r="V41" s="4" t="n">
         <v>-71.33702099999999</v>
       </c>
-      <c r="T41" s="5" t="inlineStr">
+      <c r="W41" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U41" s="5" t="inlineStr">
+      <c r="X41" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC); Noticias SLEP Puerto Cordillera</t>
         </is>
       </c>
-      <c r="V41" s="5" t="inlineStr">
+      <c r="Y41" s="5" t="inlineStr">
         <is>
           <t>Asumió por concurso de Alta Dirección Pública (SLEP, noticia 04.05.2026); la tabla del SLEP aún muestra al director anterior</t>
         </is>
@@ -4340,38 +4901,53 @@
           <t>Resolución exenta 216 de fecha 18/03/1986</t>
         </is>
       </c>
-      <c r="O42" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>Presidenta</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>www.liceobinvignat.cl</t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R42" s="7" t="n">
+      <c r="U42" s="7" t="n">
         <v>-29.963869</v>
       </c>
-      <c r="S42" s="7" t="n">
+      <c r="V42" s="7" t="n">
         <v>-71.254288</v>
       </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="X42" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr"/>
+      <c r="Y42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4438,34 +5014,49 @@
           <t>Resolución exenta 1075 de fecha 21/11/1983</t>
         </is>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Por completar</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>Informado (nómina SLEP 2026, reservada)</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Presidente</t>
+        </is>
+      </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
+          <t>Reservado</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>SLEP Puerto Cordillera, nómina presidentas/es centros de estudiantes 2026</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
           <t>Servicio Local De Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>-29.96525</v>
       </c>
-      <c r="S43" s="4" t="n">
+      <c r="V43" s="4" t="n">
         <v>-71.347221</v>
       </c>
-      <c r="T43" s="5" t="inlineStr">
+      <c r="W43" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U43" s="5" t="inlineStr">
+      <c r="X43" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -4529,21 +5120,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr"/>
-      <c r="Q44" s="8" t="inlineStr">
+      <c r="P44" s="8" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
+      <c r="S44" s="7" t="inlineStr"/>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R44" s="7" t="n"/>
-      <c r="S44" s="7" t="n"/>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="7" t="n"/>
+      <c r="W44" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr"/>
-      <c r="V44" s="8" t="inlineStr"/>
+      <c r="X44" s="8" t="inlineStr"/>
+      <c r="Y44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -4591,12 +5185,12 @@
           <t>Arauco N°1050 – Ts. Blancas</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M45" s="13" t="inlineStr">
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M45" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -4607,21 +5201,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="4" t="inlineStr"/>
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R45" s="4" t="n"/>
-      <c r="S45" s="4" t="n"/>
-      <c r="T45" s="5" t="inlineStr">
+      <c r="U45" s="4" t="n"/>
+      <c r="V45" s="4" t="n"/>
+      <c r="W45" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U45" s="5" t="inlineStr"/>
-      <c r="V45" s="5" t="inlineStr"/>
+      <c r="X45" s="5" t="inlineStr"/>
+      <c r="Y45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -4685,21 +5282,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P46" s="7" t="inlineStr"/>
-      <c r="Q46" s="8" t="inlineStr">
+      <c r="P46" s="8" t="inlineStr"/>
+      <c r="Q46" s="8" t="inlineStr"/>
+      <c r="R46" s="8" t="inlineStr"/>
+      <c r="S46" s="7" t="inlineStr"/>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R46" s="7" t="n"/>
-      <c r="S46" s="7" t="n"/>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="7" t="n"/>
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr"/>
-      <c r="V46" s="8" t="inlineStr"/>
+      <c r="X46" s="8" t="inlineStr"/>
+      <c r="Y46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -4747,12 +5347,12 @@
           <t>Camino al Faro N°50 sector Parte Alta</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M47" s="13" t="inlineStr">
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -4763,21 +5363,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="4" t="inlineStr"/>
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="5" t="inlineStr">
+      <c r="U47" s="4" t="n"/>
+      <c r="V47" s="4" t="n"/>
+      <c r="W47" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr"/>
+      <c r="X47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -4841,21 +5444,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P48" s="7" t="inlineStr"/>
-      <c r="Q48" s="8" t="inlineStr">
+      <c r="P48" s="8" t="inlineStr"/>
+      <c r="Q48" s="8" t="inlineStr"/>
+      <c r="R48" s="8" t="inlineStr"/>
+      <c r="S48" s="7" t="inlineStr"/>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R48" s="7" t="n"/>
-      <c r="S48" s="7" t="n"/>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="7" t="n"/>
+      <c r="W48" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr"/>
-      <c r="V48" s="8" t="inlineStr">
+      <c r="X48" s="8" t="inlineStr"/>
+      <c r="Y48" s="8" t="inlineStr">
         <is>
           <t>El SLEP no indica comuna; confirmar si es Coquimbo o Andacollo</t>
         </is>
@@ -4907,12 +5513,12 @@
           <t>Miraflores N°750 sector Porvenir Coquimbo</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M49" s="13" t="inlineStr">
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M49" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -4923,21 +5529,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P49" s="4" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="4" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R49" s="4" t="n"/>
-      <c r="S49" s="4" t="n"/>
-      <c r="T49" s="5" t="inlineStr">
+      <c r="U49" s="4" t="n"/>
+      <c r="V49" s="4" t="n"/>
+      <c r="W49" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr"/>
+      <c r="X49" s="5" t="inlineStr"/>
+      <c r="Y49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -5001,25 +5610,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P50" s="7" t="inlineStr"/>
-      <c r="Q50" s="8" t="inlineStr">
+      <c r="P50" s="8" t="inlineStr"/>
+      <c r="Q50" s="8" t="inlineStr"/>
+      <c r="R50" s="8" t="inlineStr"/>
+      <c r="S50" s="7" t="inlineStr"/>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R50" s="7" t="n"/>
-      <c r="S50" s="7" t="n"/>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
+      <c r="W50" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
+      <c r="X50" s="8" t="inlineStr">
         <is>
           <t>Noticias SLEP Puerto Cordillera (9.° aniv. jun. 2019; 12.° may. 2022)</t>
         </is>
       </c>
-      <c r="V50" s="8" t="inlineStr"/>
+      <c r="Y50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5067,12 +5679,12 @@
           <t>Calle Talca N°1099, sector Tierras Blancas</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M51" s="13" t="inlineStr">
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -5083,21 +5695,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="4" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R51" s="4" t="n"/>
-      <c r="S51" s="4" t="n"/>
-      <c r="T51" s="5" t="inlineStr">
+      <c r="U51" s="4" t="n"/>
+      <c r="V51" s="4" t="n"/>
+      <c r="W51" s="5" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr"/>
+      <c r="X51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -5161,21 +5776,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P52" s="7" t="inlineStr"/>
-      <c r="Q52" s="8" t="inlineStr">
+      <c r="P52" s="8" t="inlineStr"/>
+      <c r="Q52" s="8" t="inlineStr"/>
+      <c r="R52" s="8" t="inlineStr"/>
+      <c r="S52" s="7" t="inlineStr"/>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>Servicio Local de Educación Pública Puerto Cordillera</t>
         </is>
       </c>
-      <c r="R52" s="7" t="n"/>
-      <c r="S52" s="7" t="n"/>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="U52" s="7" t="n"/>
+      <c r="V52" s="7" t="n"/>
+      <c r="W52" s="8" t="inlineStr">
         <is>
           <t>SLEP Puerto Cordillera, tabla de establecimientos (act. 07.05.2026)</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr"/>
-      <c r="V52" s="8" t="inlineStr"/>
+      <c r="X52" s="8" t="inlineStr"/>
+      <c r="Y52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5227,7 +5845,7 @@
           <t>Cirujano Videla Sn</t>
         </is>
       </c>
-      <c r="L53" s="14" t="inlineStr">
+      <c r="L53" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -5242,38 +5860,41 @@
           <t>Resolución exenta 1632 de fecha 30/06/2016</t>
         </is>
       </c>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="O53" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P53" s="4" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="4" t="inlineStr">
         <is>
           <t>www.ahss.cl</t>
         </is>
       </c>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="T53" s="5" t="inlineStr">
         <is>
           <t>Aulas Hospitalarias San Sebastian E.i.e.</t>
         </is>
       </c>
-      <c r="R53" s="4" t="n">
+      <c r="U53" s="4" t="n">
         <v>-29.968593</v>
       </c>
-      <c r="S53" s="4" t="n">
+      <c r="V53" s="4" t="n">
         <v>-71.33782600000001</v>
       </c>
-      <c r="T53" s="5" t="inlineStr">
+      <c r="W53" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U53" s="5" t="inlineStr">
+      <c r="X53" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -5340,34 +5961,37 @@
           <t>Resolución exenta 1702 de fecha 26/06/2018</t>
         </is>
       </c>
-      <c r="O54" s="12" t="inlineStr">
+      <c r="O54" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="P54" s="8" t="inlineStr"/>
+      <c r="Q54" s="8" t="inlineStr"/>
+      <c r="R54" s="8" t="inlineStr"/>
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>www.cedin.cl</t>
         </is>
       </c>
-      <c r="Q54" s="8" t="inlineStr">
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Centro De Estudios Y Desarrollo Integral Del Niño</t>
         </is>
       </c>
-      <c r="R54" s="7" t="n">
+      <c r="U54" s="7" t="n">
         <v>-29.97386</v>
       </c>
-      <c r="S54" s="7" t="n">
+      <c r="V54" s="7" t="n">
         <v>-71.335342</v>
       </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="W54" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr"/>
-      <c r="V54" s="8" t="inlineStr"/>
+      <c r="X54" s="8" t="inlineStr"/>
+      <c r="Y54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5434,38 +6058,41 @@
           <t>Resolución exenta 2569 de fecha 14/12/2017</t>
         </is>
       </c>
-      <c r="O55" s="12" t="inlineStr">
+      <c r="O55" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="4" t="inlineStr">
         <is>
           <t>www.santateresa.cl</t>
         </is>
       </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="T55" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Santa Teresa De Los Andes De Sindempart</t>
         </is>
       </c>
-      <c r="R55" s="4" t="n">
+      <c r="U55" s="4" t="n">
         <v>-29.983809</v>
       </c>
-      <c r="S55" s="4" t="n">
+      <c r="V55" s="4" t="n">
         <v>-71.34273</v>
       </c>
-      <c r="T55" s="5" t="inlineStr">
+      <c r="W55" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U55" s="5" t="inlineStr">
+      <c r="X55" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V55" s="5" t="inlineStr"/>
+      <c r="Y55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -5532,38 +6159,41 @@
           <t>Resolución exenta 236 de fecha 13/02/2018</t>
         </is>
       </c>
-      <c r="O56" s="12" t="inlineStr">
+      <c r="O56" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P56" s="7" t="inlineStr">
+      <c r="P56" s="8" t="inlineStr"/>
+      <c r="Q56" s="8" t="inlineStr"/>
+      <c r="R56" s="8" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>www.ceiasanluis.cl</t>
         </is>
       </c>
-      <c r="Q56" s="8" t="inlineStr">
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional  San Luis De Coquimbo</t>
         </is>
       </c>
-      <c r="R56" s="7" t="n">
+      <c r="U56" s="7" t="n">
         <v>-29.960712</v>
       </c>
-      <c r="S56" s="7" t="n">
+      <c r="V56" s="7" t="n">
         <v>-71.34169</v>
       </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="W56" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="X56" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
+      <c r="Y56" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -5619,12 +6249,12 @@
           <t>Las Violetas Sindempart 1159</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M57" s="13" t="inlineStr">
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M57" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -5634,34 +6264,37 @@
           <t>Resolución exenta 1827 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O57" s="12" t="inlineStr">
+      <c r="O57" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="4" t="inlineStr">
         <is>
           <t>www.colegiolasvioletas.cl</t>
         </is>
       </c>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="T57" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Las Violetas</t>
         </is>
       </c>
-      <c r="R57" s="4" t="n">
+      <c r="U57" s="4" t="n">
         <v>-29.979357</v>
       </c>
-      <c r="S57" s="4" t="n">
+      <c r="V57" s="4" t="n">
         <v>-71.31021</v>
       </c>
-      <c r="T57" s="5" t="inlineStr">
+      <c r="W57" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U57" s="5" t="inlineStr"/>
-      <c r="V57" s="5" t="inlineStr">
+      <c r="X57" s="5" t="inlineStr"/>
+      <c r="Y57" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -5732,38 +6365,41 @@
           <t>Resolución exenta 1888 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O58" s="12" t="inlineStr">
+      <c r="O58" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P58" s="7" t="inlineStr">
+      <c r="P58" s="8" t="inlineStr"/>
+      <c r="Q58" s="8" t="inlineStr"/>
+      <c r="R58" s="8" t="inlineStr"/>
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>www.altacordilleracoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q58" s="8" t="inlineStr">
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Alta Cordillera</t>
         </is>
       </c>
-      <c r="R58" s="7" t="n">
+      <c r="U58" s="7" t="n">
         <v>-29.970329</v>
       </c>
-      <c r="S58" s="7" t="n">
+      <c r="V58" s="7" t="n">
         <v>-71.310333</v>
       </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="W58" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="X58" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr"/>
+      <c r="Y58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5815,7 +6451,7 @@
           <t>Regimiento Arica 700</t>
         </is>
       </c>
-      <c r="L59" s="14" t="inlineStr">
+      <c r="L59" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -5830,38 +6466,41 @@
           <t>Resolución exenta 1875 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O59" s="12" t="inlineStr">
+      <c r="O59" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P59" s="4" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>www.colegioaltazor.cl</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="T59" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Altazor  De Coquimbo</t>
         </is>
       </c>
-      <c r="R59" s="4" t="n">
+      <c r="U59" s="4" t="n">
         <v>-29.951099</v>
       </c>
-      <c r="S59" s="4" t="n">
+      <c r="V59" s="4" t="n">
         <v>-71.26696800000001</v>
       </c>
-      <c r="T59" s="5" t="inlineStr">
+      <c r="W59" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U59" s="5" t="inlineStr">
+      <c r="X59" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V59" s="5" t="inlineStr"/>
+      <c r="Y59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -5928,34 +6567,37 @@
           <t>Resolución exenta 520 de fecha 10/03/2003</t>
         </is>
       </c>
-      <c r="O60" s="12" t="inlineStr">
+      <c r="O60" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P60" s="7" t="inlineStr"/>
-      <c r="Q60" s="8" t="inlineStr">
+      <c r="P60" s="8" t="inlineStr"/>
+      <c r="Q60" s="8" t="inlineStr"/>
+      <c r="R60" s="8" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Araya, Valdés Y Araya</t>
         </is>
       </c>
-      <c r="R60" s="7" t="n">
+      <c r="U60" s="7" t="n">
         <v>-29.964081</v>
       </c>
-      <c r="S60" s="7" t="n">
+      <c r="V60" s="7" t="n">
         <v>-71.255257</v>
       </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="W60" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="X60" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V60" s="8" t="inlineStr"/>
+      <c r="Y60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -6007,12 +6649,12 @@
           <t>Avenida Matta 86</t>
         </is>
       </c>
-      <c r="L61" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M61" s="13" t="inlineStr">
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M61" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -6022,34 +6664,37 @@
           <t>Resolución exenta 1790 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O61" s="12" t="inlineStr">
+      <c r="O61" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr">
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="4" t="inlineStr">
         <is>
           <t>www.cbo.cl</t>
         </is>
       </c>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Colegio Bernardo O` Higgins- Coquimbo</t>
         </is>
       </c>
-      <c r="R61" s="4" t="n">
+      <c r="U61" s="4" t="n">
         <v>-29.96076</v>
       </c>
-      <c r="S61" s="4" t="n">
+      <c r="V61" s="4" t="n">
         <v>-71.337341</v>
       </c>
-      <c r="T61" s="5" t="inlineStr">
+      <c r="W61" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U61" s="5" t="inlineStr"/>
-      <c r="V61" s="5" t="inlineStr"/>
+      <c r="X61" s="5" t="inlineStr"/>
+      <c r="Y61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -6116,38 +6761,41 @@
           <t>Resolución exenta 1847 de fecha 29/06/2009</t>
         </is>
       </c>
-      <c r="O62" s="12" t="inlineStr">
+      <c r="O62" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P62" s="7" t="inlineStr">
+      <c r="P62" s="8" t="inlineStr"/>
+      <c r="Q62" s="8" t="inlineStr"/>
+      <c r="R62" s="8" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>www.caboalto.cl</t>
         </is>
       </c>
-      <c r="Q62" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Alta Cima</t>
         </is>
       </c>
-      <c r="R62" s="7" t="n">
+      <c r="U62" s="7" t="n">
         <v>-29.95648</v>
       </c>
-      <c r="S62" s="7" t="n">
+      <c r="V62" s="7" t="n">
         <v>-71.343193</v>
       </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="W62" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
+      <c r="X62" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V62" s="8" t="inlineStr"/>
+      <c r="Y62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -6199,7 +6847,7 @@
           <t>Los Clarines 2201</t>
         </is>
       </c>
-      <c r="L63" s="14" t="inlineStr">
+      <c r="L63" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -6214,38 +6862,41 @@
           <t>Resolución exenta 1874 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O63" s="12" t="inlineStr">
+      <c r="O63" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P63" s="4" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="R63" s="5" t="inlineStr"/>
+      <c r="S63" s="4" t="inlineStr">
         <is>
           <t>colegiocolon.cl</t>
         </is>
       </c>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>Fundación Educacional Colón</t>
         </is>
       </c>
-      <c r="R63" s="4" t="n">
+      <c r="U63" s="4" t="n">
         <v>-29.99188</v>
       </c>
-      <c r="S63" s="4" t="n">
+      <c r="V63" s="4" t="n">
         <v>-71.330429</v>
       </c>
-      <c r="T63" s="5" t="inlineStr">
+      <c r="W63" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U63" s="5" t="inlineStr">
+      <c r="X63" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V63" s="5" t="inlineStr"/>
+      <c r="Y63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -6312,38 +6963,41 @@
           <t>Resolución exenta 1853 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O64" s="12" t="inlineStr">
+      <c r="O64" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P64" s="7" t="inlineStr">
+      <c r="P64" s="8" t="inlineStr"/>
+      <c r="Q64" s="8" t="inlineStr"/>
+      <c r="R64" s="8" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>discoveryschool.cl</t>
         </is>
       </c>
-      <c r="Q64" s="8" t="inlineStr">
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Aventura</t>
         </is>
       </c>
-      <c r="R64" s="7" t="n">
+      <c r="U64" s="7" t="n">
         <v>-29.967319</v>
       </c>
-      <c r="S64" s="7" t="n">
+      <c r="V64" s="7" t="n">
         <v>-71.344543</v>
       </c>
-      <c r="T64" s="8" t="inlineStr">
+      <c r="W64" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
+      <c r="X64" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V64" s="8" t="inlineStr"/>
+      <c r="Y64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -6395,12 +7049,12 @@
           <t>Pedro Montt 220. El Llano 220</t>
         </is>
       </c>
-      <c r="L65" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M65" s="13" t="inlineStr">
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M65" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -6410,30 +7064,33 @@
           <t>Resolución exenta 2179 de fecha 06/08/2018</t>
         </is>
       </c>
-      <c r="O65" s="12" t="inlineStr">
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P65" s="4" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr"/>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="4" t="inlineStr"/>
+      <c r="T65" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Domingo Faustino Sarmiento</t>
         </is>
       </c>
-      <c r="R65" s="4" t="n">
+      <c r="U65" s="4" t="n">
         <v>-29.961691</v>
       </c>
-      <c r="S65" s="4" t="n">
+      <c r="V65" s="4" t="n">
         <v>-71.34047700000001</v>
       </c>
-      <c r="T65" s="5" t="inlineStr">
+      <c r="W65" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U65" s="5" t="inlineStr"/>
-      <c r="V65" s="5" t="inlineStr"/>
+      <c r="X65" s="5" t="inlineStr"/>
+      <c r="Y65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -6500,34 +7157,37 @@
           <t>Resolución exenta 1929 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O66" s="12" t="inlineStr">
+      <c r="O66" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P66" s="7" t="inlineStr"/>
-      <c r="Q66" s="8" t="inlineStr">
+      <c r="P66" s="8" t="inlineStr"/>
+      <c r="Q66" s="8" t="inlineStr"/>
+      <c r="R66" s="8" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr"/>
+      <c r="T66" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Colegio Español</t>
         </is>
       </c>
-      <c r="R66" s="7" t="n">
+      <c r="U66" s="7" t="n">
         <v>-29.966181</v>
       </c>
-      <c r="S66" s="7" t="n">
+      <c r="V66" s="7" t="n">
         <v>-71.341133</v>
       </c>
-      <c r="T66" s="8" t="inlineStr">
+      <c r="W66" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U66" s="8" t="inlineStr">
+      <c r="X66" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V66" s="8" t="inlineStr"/>
+      <c r="Y66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -6594,38 +7254,41 @@
           <t>Resolución exenta 1785 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O67" s="12" t="inlineStr">
+      <c r="O67" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P67" s="4" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="4" t="inlineStr">
         <is>
           <t>www.eusebiolillo.com</t>
         </is>
       </c>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="T67" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Eusebio Lillo</t>
         </is>
       </c>
-      <c r="R67" s="4" t="n">
+      <c r="U67" s="4" t="n">
         <v>-29.997339</v>
       </c>
-      <c r="S67" s="4" t="n">
+      <c r="V67" s="4" t="n">
         <v>-71.330879</v>
       </c>
-      <c r="T67" s="5" t="inlineStr">
+      <c r="W67" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U67" s="5" t="inlineStr">
+      <c r="X67" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V67" s="5" t="inlineStr"/>
+      <c r="Y67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -6692,38 +7355,41 @@
           <t>Resolución exenta 0765 de fecha 27/06/1990</t>
         </is>
       </c>
-      <c r="O68" s="12" t="inlineStr">
+      <c r="O68" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P68" s="7" t="inlineStr">
+      <c r="P68" s="8" t="inlineStr"/>
+      <c r="Q68" s="8" t="inlineStr"/>
+      <c r="R68" s="8" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr">
         <is>
           <t>www.francisschool.cl</t>
         </is>
       </c>
-      <c r="Q68" s="8" t="inlineStr">
+      <c r="T68" s="8" t="inlineStr">
         <is>
           <t>Fundación Educacional Francis School</t>
         </is>
       </c>
-      <c r="R68" s="7" t="n">
+      <c r="U68" s="7" t="n">
         <v>-29.977051</v>
       </c>
-      <c r="S68" s="7" t="n">
+      <c r="V68" s="7" t="n">
         <v>-71.34169</v>
       </c>
-      <c r="T68" s="8" t="inlineStr">
+      <c r="W68" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U68" s="8" t="inlineStr">
+      <c r="X68" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V68" s="8" t="inlineStr"/>
+      <c r="Y68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -6775,7 +7441,7 @@
           <t>Eduardo Mallea 401</t>
         </is>
       </c>
-      <c r="L69" s="14" t="inlineStr">
+      <c r="L69" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -6790,38 +7456,41 @@
           <t>Resolución exenta 1791 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O69" s="12" t="inlineStr">
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P69" s="4" t="inlineStr">
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr"/>
+      <c r="S69" s="4" t="inlineStr">
         <is>
           <t>goldenhindschool.cl</t>
         </is>
       </c>
-      <c r="Q69" s="5" t="inlineStr">
+      <c r="T69" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Masadi</t>
         </is>
       </c>
-      <c r="R69" s="4" t="n">
+      <c r="U69" s="4" t="n">
         <v>-29.98847</v>
       </c>
-      <c r="S69" s="4" t="n">
+      <c r="V69" s="4" t="n">
         <v>-71.332626</v>
       </c>
-      <c r="T69" s="5" t="inlineStr">
+      <c r="W69" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U69" s="5" t="inlineStr">
+      <c r="X69" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V69" s="5" t="inlineStr"/>
+      <c r="Y69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -6888,34 +7557,37 @@
           <t>Resolución exenta 4056 de fecha 04/12/2007</t>
         </is>
       </c>
-      <c r="O70" s="12" t="inlineStr">
+      <c r="O70" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P70" s="7" t="inlineStr">
+      <c r="P70" s="8" t="inlineStr"/>
+      <c r="Q70" s="8" t="inlineStr"/>
+      <c r="R70" s="8" t="inlineStr"/>
+      <c r="S70" s="7" t="inlineStr">
         <is>
           <t>www.colegiohellenkeller.cl</t>
         </is>
       </c>
-      <c r="Q70" s="8" t="inlineStr">
+      <c r="T70" s="8" t="inlineStr">
         <is>
           <t>Fundación Educacional Colegio Hellen Keller</t>
         </is>
       </c>
-      <c r="R70" s="7" t="n">
+      <c r="U70" s="7" t="n">
         <v>-29.956511</v>
       </c>
-      <c r="S70" s="7" t="n">
+      <c r="V70" s="7" t="n">
         <v>-71.27716100000001</v>
       </c>
-      <c r="T70" s="8" t="inlineStr">
+      <c r="W70" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U70" s="8" t="inlineStr"/>
-      <c r="V70" s="8" t="inlineStr">
+      <c r="X70" s="8" t="inlineStr"/>
+      <c r="Y70" s="8" t="inlineStr">
         <is>
           <t>Prefijo de Santiago: verificar</t>
         </is>
@@ -6971,7 +7643,7 @@
           <t>Parque Nacional Fray Jorge 1153</t>
         </is>
       </c>
-      <c r="L71" s="14" t="inlineStr">
+      <c r="L71" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -6986,38 +7658,41 @@
           <t>Resolución exenta 567 de fecha 15/03/2018</t>
         </is>
       </c>
-      <c r="O71" s="12" t="inlineStr">
+      <c r="O71" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P71" s="4" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr"/>
+      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="R71" s="5" t="inlineStr"/>
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>www.colegiohorizontes.cl</t>
         </is>
       </c>
-      <c r="Q71" s="5" t="inlineStr">
+      <c r="T71" s="5" t="inlineStr">
         <is>
           <t>Fundación  Educacional Nuevos Horizontes</t>
         </is>
       </c>
-      <c r="R71" s="4" t="n">
+      <c r="U71" s="4" t="n">
         <v>-29.97299</v>
       </c>
-      <c r="S71" s="4" t="n">
+      <c r="V71" s="4" t="n">
         <v>-71.254204</v>
       </c>
-      <c r="T71" s="5" t="inlineStr">
+      <c r="W71" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U71" s="5" t="inlineStr">
+      <c r="X71" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V71" s="5" t="inlineStr"/>
+      <c r="Y71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -7084,34 +7759,37 @@
           <t>Resolución exenta 1894 de fecha 29/06/2006</t>
         </is>
       </c>
-      <c r="O72" s="12" t="inlineStr">
+      <c r="O72" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P72" s="7" t="inlineStr">
+      <c r="P72" s="8" t="inlineStr"/>
+      <c r="Q72" s="8" t="inlineStr"/>
+      <c r="R72" s="8" t="inlineStr"/>
+      <c r="S72" s="7" t="inlineStr">
         <is>
           <t>www.josemarti.cl</t>
         </is>
       </c>
-      <c r="Q72" s="8" t="inlineStr">
+      <c r="T72" s="8" t="inlineStr">
         <is>
           <t>José Marti Corporacion Educacional</t>
         </is>
       </c>
-      <c r="R72" s="7" t="n">
+      <c r="U72" s="7" t="n">
         <v>-29.970831</v>
       </c>
-      <c r="S72" s="7" t="n">
+      <c r="V72" s="7" t="n">
         <v>-71.331367</v>
       </c>
-      <c r="T72" s="8" t="inlineStr">
+      <c r="W72" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U72" s="8" t="inlineStr"/>
-      <c r="V72" s="8" t="inlineStr"/>
+      <c r="X72" s="8" t="inlineStr"/>
+      <c r="Y72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -7163,12 +7841,12 @@
           <t>Los Espinos Sur 2715 El Sauce Miramar</t>
         </is>
       </c>
-      <c r="L73" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M73" s="13" t="inlineStr">
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -7178,34 +7856,37 @@
           <t>Resolución exenta 1882 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O73" s="12" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P73" s="4" t="inlineStr">
+      <c r="P73" s="5" t="inlineStr"/>
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr"/>
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>colegiomanuelmontt.cl</t>
         </is>
       </c>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="T73" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Manuel Montt</t>
         </is>
       </c>
-      <c r="R73" s="4" t="n">
+      <c r="U73" s="4" t="n">
         <v>-29.999411</v>
       </c>
-      <c r="S73" s="4" t="n">
+      <c r="V73" s="4" t="n">
         <v>-71.33577699999999</v>
       </c>
-      <c r="T73" s="5" t="inlineStr">
+      <c r="W73" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U73" s="5" t="inlineStr"/>
-      <c r="V73" s="5" t="inlineStr">
+      <c r="X73" s="5" t="inlineStr"/>
+      <c r="Y73" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -7276,34 +7957,37 @@
           <t>Resolución exenta 843 de fecha 09/05/2002</t>
         </is>
       </c>
-      <c r="O74" s="12" t="inlineStr">
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P74" s="7" t="inlineStr">
+      <c r="P74" s="8" t="inlineStr"/>
+      <c r="Q74" s="8" t="inlineStr"/>
+      <c r="R74" s="8" t="inlineStr"/>
+      <c r="S74" s="7" t="inlineStr">
         <is>
           <t>www.mariaeduca.cl</t>
         </is>
       </c>
-      <c r="Q74" s="8" t="inlineStr">
+      <c r="T74" s="8" t="inlineStr">
         <is>
           <t>Fundacion Maria Educa</t>
         </is>
       </c>
-      <c r="R74" s="7" t="n">
+      <c r="U74" s="7" t="n">
         <v>-29.97242</v>
       </c>
-      <c r="S74" s="7" t="n">
+      <c r="V74" s="7" t="n">
         <v>-71.256821</v>
       </c>
-      <c r="T74" s="8" t="inlineStr">
+      <c r="W74" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U74" s="8" t="inlineStr"/>
-      <c r="V74" s="8" t="inlineStr"/>
+      <c r="X74" s="8" t="inlineStr"/>
+      <c r="Y74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -7355,7 +8039,7 @@
           <t>Luis Torres Araya , Tierras Blancas 14</t>
         </is>
       </c>
-      <c r="L75" s="14" t="inlineStr">
+      <c r="L75" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -7370,38 +8054,41 @@
           <t>Resolución exenta 1832 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O75" s="12" t="inlineStr">
+      <c r="O75" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr">
+      <c r="P75" s="5" t="inlineStr"/>
+      <c r="Q75" s="5" t="inlineStr"/>
+      <c r="R75" s="5" t="inlineStr"/>
+      <c r="S75" s="4" t="inlineStr">
         <is>
           <t>www.colegiomariadeandacollo.cl</t>
         </is>
       </c>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="T75" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional María De Andacollo</t>
         </is>
       </c>
-      <c r="R75" s="4" t="n">
+      <c r="U75" s="4" t="n">
         <v>-29.957371</v>
       </c>
-      <c r="S75" s="4" t="n">
+      <c r="V75" s="4" t="n">
         <v>-71.247704</v>
       </c>
-      <c r="T75" s="5" t="inlineStr">
+      <c r="W75" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U75" s="5" t="inlineStr">
+      <c r="X75" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V75" s="5" t="inlineStr"/>
+      <c r="Y75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -7468,38 +8155,41 @@
           <t>Resolución exenta 993 de fecha 15/05/2017</t>
         </is>
       </c>
-      <c r="O76" s="12" t="inlineStr">
+      <c r="O76" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P76" s="7" t="inlineStr">
+      <c r="P76" s="8" t="inlineStr"/>
+      <c r="Q76" s="8" t="inlineStr"/>
+      <c r="R76" s="8" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr">
         <is>
           <t>www.escuelametodista.cl</t>
         </is>
       </c>
-      <c r="Q76" s="8" t="inlineStr">
+      <c r="T76" s="8" t="inlineStr">
         <is>
           <t>Corporacion Metodista</t>
         </is>
       </c>
-      <c r="R76" s="7" t="n">
+      <c r="U76" s="7" t="n">
         <v>-29.957479</v>
       </c>
-      <c r="S76" s="7" t="n">
+      <c r="V76" s="7" t="n">
         <v>-71.343391</v>
       </c>
-      <c r="T76" s="8" t="inlineStr">
+      <c r="W76" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U76" s="8" t="inlineStr">
+      <c r="X76" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V76" s="8" t="inlineStr"/>
+      <c r="Y76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -7551,12 +8241,12 @@
           <t>Subteniente Héctor Lacrampette 114</t>
         </is>
       </c>
-      <c r="L77" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M77" s="13" t="inlineStr">
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M77" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -7566,34 +8256,37 @@
           <t>Resolución exenta 13525 de fecha 02/06/2003</t>
         </is>
       </c>
-      <c r="O77" s="12" t="inlineStr">
+      <c r="O77" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P77" s="4" t="inlineStr">
+      <c r="P77" s="5" t="inlineStr"/>
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr"/>
+      <c r="S77" s="4" t="inlineStr">
         <is>
           <t>www.colegioadultosolimpo.cl</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="T77" s="5" t="inlineStr">
         <is>
           <t>Corporacion Manantial</t>
         </is>
       </c>
-      <c r="R77" s="4" t="n">
+      <c r="U77" s="4" t="n">
         <v>-29.957752</v>
       </c>
-      <c r="S77" s="4" t="n">
+      <c r="V77" s="4" t="n">
         <v>-71.25394</v>
       </c>
-      <c r="T77" s="5" t="inlineStr">
+      <c r="W77" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U77" s="5" t="inlineStr"/>
-      <c r="V77" s="5" t="inlineStr">
+      <c r="X77" s="5" t="inlineStr"/>
+      <c r="Y77" s="5" t="inlineStr">
         <is>
           <t>Prefijo de Santiago: verificar</t>
         </is>
@@ -7669,29 +8362,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P78" s="7" t="inlineStr"/>
-      <c r="Q78" s="8" t="inlineStr">
+      <c r="P78" s="8" t="inlineStr"/>
+      <c r="Q78" s="8" t="inlineStr"/>
+      <c r="R78" s="8" t="inlineStr"/>
+      <c r="S78" s="7" t="inlineStr"/>
+      <c r="T78" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Dayca</t>
         </is>
       </c>
-      <c r="R78" s="7" t="n">
+      <c r="U78" s="7" t="n">
         <v>-29.9868</v>
       </c>
-      <c r="S78" s="7" t="n">
+      <c r="V78" s="7" t="n">
         <v>-71.36073</v>
       </c>
-      <c r="T78" s="8" t="inlineStr">
+      <c r="W78" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U78" s="8" t="inlineStr">
+      <c r="X78" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V78" s="8" t="inlineStr">
+      <c r="Y78" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -7747,7 +8443,7 @@
           <t>Av. Pdte. Arturo Alessandri 1859</t>
         </is>
       </c>
-      <c r="L79" s="14" t="inlineStr">
+      <c r="L79" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -7762,38 +8458,41 @@
           <t>Resolución exenta 1296 de fecha 09/05/2018</t>
         </is>
       </c>
-      <c r="O79" s="12" t="inlineStr">
+      <c r="O79" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P79" s="4" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr"/>
+      <c r="Q79" s="5" t="inlineStr"/>
+      <c r="R79" s="5" t="inlineStr"/>
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>www.colegiokomvux.cl</t>
         </is>
       </c>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="T79" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Colegio Komvux</t>
         </is>
       </c>
-      <c r="R79" s="4" t="n">
+      <c r="U79" s="4" t="n">
         <v>-29.983101</v>
       </c>
-      <c r="S79" s="4" t="n">
+      <c r="V79" s="4" t="n">
         <v>-71.33429700000001</v>
       </c>
-      <c r="T79" s="5" t="inlineStr">
+      <c r="W79" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U79" s="5" t="inlineStr">
+      <c r="X79" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V79" s="5" t="inlineStr">
+      <c r="Y79" s="5" t="inlineStr">
         <is>
           <t>Prefijo de Santiago: verificar</t>
         </is>
@@ -7864,34 +8563,37 @@
           <t>Resolución exenta 317 de fecha 07/04/1987</t>
         </is>
       </c>
-      <c r="O80" s="12" t="inlineStr">
+      <c r="O80" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P80" s="7" t="inlineStr">
+      <c r="P80" s="8" t="inlineStr"/>
+      <c r="Q80" s="8" t="inlineStr"/>
+      <c r="R80" s="8" t="inlineStr"/>
+      <c r="S80" s="7" t="inlineStr">
         <is>
           <t>calasanztb.cl</t>
         </is>
       </c>
-      <c r="Q80" s="8" t="inlineStr">
+      <c r="T80" s="8" t="inlineStr">
         <is>
           <t>Pio Instituto Hijas De Maria Religiosas De Las Escuelas Pias</t>
         </is>
       </c>
-      <c r="R80" s="7" t="n">
+      <c r="U80" s="7" t="n">
         <v>-29.966249</v>
       </c>
-      <c r="S80" s="7" t="n">
+      <c r="V80" s="7" t="n">
         <v>-71.256844</v>
       </c>
-      <c r="T80" s="8" t="inlineStr">
+      <c r="W80" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U80" s="8" t="inlineStr"/>
-      <c r="V80" s="8" t="inlineStr"/>
+      <c r="X80" s="8" t="inlineStr"/>
+      <c r="Y80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -7943,12 +8645,12 @@
           <t>Abtao 22</t>
         </is>
       </c>
-      <c r="L81" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr">
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -7958,34 +8660,37 @@
           <t>Resolución exenta 01240 de fecha 15/09/1982</t>
         </is>
       </c>
-      <c r="O81" s="12" t="inlineStr">
+      <c r="O81" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P81" s="4" t="inlineStr">
+      <c r="P81" s="5" t="inlineStr"/>
+      <c r="Q81" s="5" t="inlineStr"/>
+      <c r="R81" s="5" t="inlineStr"/>
+      <c r="S81" s="4" t="inlineStr">
         <is>
           <t>www.colegiogabrielamistralcoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q81" s="5" t="inlineStr">
+      <c r="T81" s="5" t="inlineStr">
         <is>
           <t>Corporación Colegio Gabriela Mistral De Coquimbo</t>
         </is>
       </c>
-      <c r="R81" s="4" t="n">
+      <c r="U81" s="4" t="n">
         <v>-29.963671</v>
       </c>
-      <c r="S81" s="4" t="n">
+      <c r="V81" s="4" t="n">
         <v>-71.339043</v>
       </c>
-      <c r="T81" s="5" t="inlineStr">
+      <c r="W81" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U81" s="5" t="inlineStr"/>
-      <c r="V81" s="5" t="inlineStr"/>
+      <c r="X81" s="5" t="inlineStr"/>
+      <c r="Y81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -8052,38 +8757,41 @@
           <t>Resolución exenta 1887 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O82" s="12" t="inlineStr">
+      <c r="O82" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P82" s="7" t="inlineStr">
+      <c r="P82" s="8" t="inlineStr"/>
+      <c r="Q82" s="8" t="inlineStr"/>
+      <c r="R82" s="8" t="inlineStr"/>
+      <c r="S82" s="7" t="inlineStr">
         <is>
           <t>www.davincicoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q82" s="8" t="inlineStr">
+      <c r="T82" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Peñuelas</t>
         </is>
       </c>
-      <c r="R82" s="7" t="n">
+      <c r="U82" s="7" t="n">
         <v>-29.95256</v>
       </c>
-      <c r="S82" s="7" t="n">
+      <c r="V82" s="7" t="n">
         <v>-71.270157</v>
       </c>
-      <c r="T82" s="8" t="inlineStr">
+      <c r="W82" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U82" s="8" t="inlineStr">
+      <c r="X82" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V82" s="8" t="inlineStr"/>
+      <c r="Y82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -8135,12 +8843,12 @@
           <t>Lincoyan 065</t>
         </is>
       </c>
-      <c r="L83" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M83" s="13" t="inlineStr">
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -8150,34 +8858,37 @@
           <t>Resolución exenta 560 de fecha 04/04/2017</t>
         </is>
       </c>
-      <c r="O83" s="12" t="inlineStr">
+      <c r="O83" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P83" s="4" t="inlineStr">
+      <c r="P83" s="5" t="inlineStr"/>
+      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr"/>
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>www.corporacionsfj.cl</t>
         </is>
       </c>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="T83" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional San Francisco Javier</t>
         </is>
       </c>
-      <c r="R83" s="4" t="n">
+      <c r="U83" s="4" t="n">
         <v>-29.9601</v>
       </c>
-      <c r="S83" s="4" t="n">
+      <c r="V83" s="4" t="n">
         <v>-71.343559</v>
       </c>
-      <c r="T83" s="5" t="inlineStr">
+      <c r="W83" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U83" s="5" t="inlineStr"/>
-      <c r="V83" s="5" t="inlineStr">
+      <c r="X83" s="5" t="inlineStr"/>
+      <c r="Y83" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -8248,30 +8959,33 @@
           <t>Resolución exenta 22254 de fecha 23/11/2017</t>
         </is>
       </c>
-      <c r="O84" s="12" t="inlineStr">
+      <c r="O84" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P84" s="7" t="inlineStr"/>
-      <c r="Q84" s="8" t="inlineStr">
+      <c r="P84" s="8" t="inlineStr"/>
+      <c r="Q84" s="8" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr"/>
+      <c r="S84" s="7" t="inlineStr"/>
+      <c r="T84" s="8" t="inlineStr">
         <is>
           <t>San Gabriel Arcangel E.i.e.</t>
         </is>
       </c>
-      <c r="R84" s="7" t="n">
+      <c r="U84" s="7" t="n">
         <v>-29.962021</v>
       </c>
-      <c r="S84" s="7" t="n">
+      <c r="V84" s="7" t="n">
         <v>-71.339333</v>
       </c>
-      <c r="T84" s="8" t="inlineStr">
+      <c r="W84" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="8" t="inlineStr">
+      <c r="X84" s="8" t="inlineStr"/>
+      <c r="Y84" s="8" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -8342,38 +9056,41 @@
           <t>Resolución exenta 17 de fecha 07/01/1982</t>
         </is>
       </c>
-      <c r="O85" s="12" t="inlineStr">
+      <c r="O85" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P85" s="4" t="inlineStr">
+      <c r="P85" s="5" t="inlineStr"/>
+      <c r="Q85" s="5" t="inlineStr"/>
+      <c r="R85" s="5" t="inlineStr"/>
+      <c r="S85" s="4" t="inlineStr">
         <is>
           <t>www.sanignacio-coquimbo.cl</t>
         </is>
       </c>
-      <c r="Q85" s="5" t="inlineStr">
+      <c r="T85" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional San Ignacio De Coquimbo</t>
         </is>
       </c>
-      <c r="R85" s="4" t="n">
+      <c r="U85" s="4" t="n">
         <v>-29.98802</v>
       </c>
-      <c r="S85" s="4" t="n">
+      <c r="V85" s="4" t="n">
         <v>-71.334671</v>
       </c>
-      <c r="T85" s="5" t="inlineStr">
+      <c r="W85" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U85" s="5" t="inlineStr">
+      <c r="X85" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V85" s="5" t="inlineStr"/>
+      <c r="Y85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -8440,30 +9157,33 @@
           <t>Resolución exenta 1603 de fecha 25/07/2017</t>
         </is>
       </c>
-      <c r="O86" s="12" t="inlineStr">
+      <c r="O86" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P86" s="7" t="inlineStr"/>
-      <c r="Q86" s="8" t="inlineStr">
+      <c r="P86" s="8" t="inlineStr"/>
+      <c r="Q86" s="8" t="inlineStr"/>
+      <c r="R86" s="8" t="inlineStr"/>
+      <c r="S86" s="7" t="inlineStr"/>
+      <c r="T86" s="8" t="inlineStr">
         <is>
           <t>Corporacion Educacional Colegio Tongoy</t>
         </is>
       </c>
-      <c r="R86" s="7" t="n">
+      <c r="U86" s="7" t="n">
         <v>-30.260481</v>
       </c>
-      <c r="S86" s="7" t="n">
+      <c r="V86" s="7" t="n">
         <v>-71.490852</v>
       </c>
-      <c r="T86" s="8" t="inlineStr">
+      <c r="W86" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U86" s="8" t="inlineStr"/>
-      <c r="V86" s="8" t="inlineStr"/>
+      <c r="X86" s="8" t="inlineStr"/>
+      <c r="Y86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -8515,7 +9235,7 @@
           <t>Avenida La Cantera 610</t>
         </is>
       </c>
-      <c r="L87" s="14" t="inlineStr">
+      <c r="L87" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -8530,38 +9250,41 @@
           <t>Resolución exenta 1788 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O87" s="12" t="inlineStr">
+      <c r="O87" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P87" s="4" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr"/>
+      <c r="Q87" s="5" t="inlineStr"/>
+      <c r="R87" s="5" t="inlineStr"/>
+      <c r="S87" s="4" t="inlineStr">
         <is>
           <t>www.colegiorakiduam.cl</t>
         </is>
       </c>
-      <c r="Q87" s="5" t="inlineStr">
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>Fundación Educacional Rakiduam</t>
         </is>
       </c>
-      <c r="R87" s="4" t="n">
+      <c r="U87" s="4" t="n">
         <v>-29.9666</v>
       </c>
-      <c r="S87" s="4" t="n">
+      <c r="V87" s="4" t="n">
         <v>-71.31031</v>
       </c>
-      <c r="T87" s="5" t="inlineStr">
+      <c r="W87" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U87" s="5" t="inlineStr">
+      <c r="X87" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V87" s="5" t="inlineStr">
+      <c r="Y87" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -8632,34 +9355,37 @@
           <t>Resolución exenta 578 de fecha 16/03/2018</t>
         </is>
       </c>
-      <c r="O88" s="12" t="inlineStr">
+      <c r="O88" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P88" s="7" t="inlineStr">
+      <c r="P88" s="8" t="inlineStr"/>
+      <c r="Q88" s="8" t="inlineStr"/>
+      <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="7" t="inlineStr">
         <is>
           <t>www.colegiosanlorenzolacantera.cl</t>
         </is>
       </c>
-      <c r="Q88" s="8" t="inlineStr">
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>Corporación Colegio San Lorenzo  De Coquimbo</t>
         </is>
       </c>
-      <c r="R88" s="7" t="n">
+      <c r="U88" s="7" t="n">
         <v>-29.97743</v>
       </c>
-      <c r="S88" s="7" t="n">
+      <c r="V88" s="7" t="n">
         <v>-71.29338799999999</v>
       </c>
-      <c r="T88" s="8" t="inlineStr">
+      <c r="W88" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U88" s="8" t="inlineStr"/>
-      <c r="V88" s="8" t="inlineStr"/>
+      <c r="X88" s="8" t="inlineStr"/>
+      <c r="Y88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -8711,12 +9437,12 @@
           <t>Avda Ossandon 350</t>
         </is>
       </c>
-      <c r="L89" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M89" s="13" t="inlineStr">
+      <c r="L89" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -8726,34 +9452,37 @@
           <t>Resolución exenta 238 de fecha 13/02/2018</t>
         </is>
       </c>
-      <c r="O89" s="12" t="inlineStr">
+      <c r="O89" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P89" s="4" t="inlineStr">
+      <c r="P89" s="5" t="inlineStr"/>
+      <c r="Q89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr"/>
+      <c r="S89" s="4" t="inlineStr">
         <is>
           <t>www.instagram.com/colegio_sanluis_coquimbo/</t>
         </is>
       </c>
-      <c r="Q89" s="5" t="inlineStr">
+      <c r="T89" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional  San Luis De Coquimbo</t>
         </is>
       </c>
-      <c r="R89" s="4" t="n">
+      <c r="U89" s="4" t="n">
         <v>-29.96158</v>
       </c>
-      <c r="S89" s="4" t="n">
+      <c r="V89" s="4" t="n">
         <v>-71.342957</v>
       </c>
-      <c r="T89" s="5" t="inlineStr">
+      <c r="W89" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U89" s="5" t="inlineStr"/>
-      <c r="V89" s="5" t="inlineStr"/>
+      <c r="X89" s="5" t="inlineStr"/>
+      <c r="Y89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -8820,38 +9549,41 @@
           <t>Resolución exenta 756 de fecha 01/03/1999</t>
         </is>
       </c>
-      <c r="O90" s="12" t="inlineStr">
+      <c r="O90" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P90" s="7" t="inlineStr">
+      <c r="P90" s="8" t="inlineStr"/>
+      <c r="Q90" s="8" t="inlineStr"/>
+      <c r="R90" s="8" t="inlineStr"/>
+      <c r="S90" s="7" t="inlineStr">
         <is>
           <t>www.colegiosantafamilia.cl</t>
         </is>
       </c>
-      <c r="Q90" s="8" t="inlineStr">
+      <c r="T90" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional San Guillermo</t>
         </is>
       </c>
-      <c r="R90" s="7" t="n">
+      <c r="U90" s="7" t="n">
         <v>-29.99054</v>
       </c>
-      <c r="S90" s="7" t="n">
+      <c r="V90" s="7" t="n">
         <v>-71.334129</v>
       </c>
-      <c r="T90" s="8" t="inlineStr">
+      <c r="W90" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U90" s="8" t="inlineStr">
+      <c r="X90" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V90" s="8" t="inlineStr"/>
+      <c r="Y90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -8903,12 +9635,12 @@
           <t>Avda Videla 235</t>
         </is>
       </c>
-      <c r="L91" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M91" s="13" t="inlineStr">
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -8918,34 +9650,37 @@
           <t>Resolución exenta 1856 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O91" s="12" t="inlineStr">
+      <c r="O91" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P91" s="4" t="inlineStr">
+      <c r="P91" s="5" t="inlineStr"/>
+      <c r="Q91" s="5" t="inlineStr"/>
+      <c r="R91" s="5" t="inlineStr"/>
+      <c r="S91" s="4" t="inlineStr">
         <is>
           <t>w.w.w.shcc.cl</t>
         </is>
       </c>
-      <c r="Q91" s="5" t="inlineStr">
+      <c r="T91" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Santa Helena College</t>
         </is>
       </c>
-      <c r="R91" s="4" t="n">
+      <c r="U91" s="4" t="n">
         <v>-29.96242</v>
       </c>
-      <c r="S91" s="4" t="n">
+      <c r="V91" s="4" t="n">
         <v>-71.337532</v>
       </c>
-      <c r="T91" s="5" t="inlineStr">
+      <c r="W91" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U91" s="5" t="inlineStr"/>
-      <c r="V91" s="5" t="inlineStr"/>
+      <c r="X91" s="5" t="inlineStr"/>
+      <c r="Y91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -9012,34 +9747,37 @@
           <t>Resolución exenta 1067 de fecha 16/06/1993</t>
         </is>
       </c>
-      <c r="O92" s="12" t="inlineStr">
+      <c r="O92" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P92" s="7" t="inlineStr">
+      <c r="P92" s="8" t="inlineStr"/>
+      <c r="Q92" s="8" t="inlineStr"/>
+      <c r="R92" s="8" t="inlineStr"/>
+      <c r="S92" s="7" t="inlineStr">
         <is>
           <t>www.smbelenfranciscanas.cl</t>
         </is>
       </c>
-      <c r="Q92" s="8" t="inlineStr">
+      <c r="T92" s="8" t="inlineStr">
         <is>
           <t>Hermanas Franciscanas Misioneras De Jesus</t>
         </is>
       </c>
-      <c r="R92" s="7" t="n">
+      <c r="U92" s="7" t="n">
         <v>-29.98431</v>
       </c>
-      <c r="S92" s="7" t="n">
+      <c r="V92" s="7" t="n">
         <v>-71.34538999999999</v>
       </c>
-      <c r="T92" s="8" t="inlineStr">
+      <c r="W92" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="8" t="inlineStr">
+      <c r="X92" s="8" t="inlineStr"/>
+      <c r="Y92" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -9110,38 +9848,41 @@
           <t>Resolución exenta 3760 de fecha 01/01/2002</t>
         </is>
       </c>
-      <c r="O93" s="12" t="inlineStr">
+      <c r="O93" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P93" s="4" t="inlineStr">
+      <c r="P93" s="5" t="inlineStr"/>
+      <c r="Q93" s="5" t="inlineStr"/>
+      <c r="R93" s="5" t="inlineStr"/>
+      <c r="S93" s="4" t="inlineStr">
         <is>
           <t>www.santamariadelrefugio.com</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr">
+      <c r="T93" s="5" t="inlineStr">
         <is>
           <t>Hermanas Franciscanas Misioneras De Jesus</t>
         </is>
       </c>
-      <c r="R93" s="4" t="n">
+      <c r="U93" s="4" t="n">
         <v>-29.94212</v>
       </c>
-      <c r="S93" s="4" t="n">
+      <c r="V93" s="4" t="n">
         <v>-71.341911</v>
       </c>
-      <c r="T93" s="5" t="inlineStr">
+      <c r="W93" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U93" s="5" t="inlineStr">
+      <c r="X93" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V93" s="5" t="inlineStr"/>
+      <c r="Y93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -9208,34 +9949,37 @@
           <t>Resolución exenta 5012 de fecha 19/11/1981</t>
         </is>
       </c>
-      <c r="O94" s="12" t="inlineStr">
+      <c r="O94" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P94" s="7" t="inlineStr">
+      <c r="P94" s="8" t="inlineStr"/>
+      <c r="Q94" s="8" t="inlineStr"/>
+      <c r="R94" s="8" t="inlineStr"/>
+      <c r="S94" s="7" t="inlineStr">
         <is>
           <t>www.colegiosantamartacoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q94" s="8" t="inlineStr">
+      <c r="T94" s="8" t="inlineStr">
         <is>
           <t>Fundacion Educacional Colegio Santa Marta Coq</t>
         </is>
       </c>
-      <c r="R94" s="7" t="n">
+      <c r="U94" s="7" t="n">
         <v>-29.96142</v>
       </c>
-      <c r="S94" s="7" t="n">
+      <c r="V94" s="7" t="n">
         <v>-71.34729</v>
       </c>
-      <c r="T94" s="8" t="inlineStr">
+      <c r="W94" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U94" s="8" t="inlineStr"/>
-      <c r="V94" s="8" t="inlineStr"/>
+      <c r="X94" s="8" t="inlineStr"/>
+      <c r="Y94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -9302,38 +10046,41 @@
           <t>Resolución exenta 1785 de fecha 12/09/2016</t>
         </is>
       </c>
-      <c r="O95" s="12" t="inlineStr">
+      <c r="O95" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P95" s="4" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr"/>
+      <c r="Q95" s="5" t="inlineStr"/>
+      <c r="R95" s="5" t="inlineStr"/>
+      <c r="S95" s="4" t="inlineStr">
         <is>
           <t>www.colegioaltue.cl</t>
         </is>
       </c>
-      <c r="Q95" s="5" t="inlineStr">
+      <c r="T95" s="5" t="inlineStr">
         <is>
           <t>Corporaciòn Educacional Cristo De La Misericordia</t>
         </is>
       </c>
-      <c r="R95" s="4" t="n">
+      <c r="U95" s="4" t="n">
         <v>-29.953421</v>
       </c>
-      <c r="S95" s="4" t="n">
+      <c r="V95" s="4" t="n">
         <v>-71.24812300000001</v>
       </c>
-      <c r="T95" s="5" t="inlineStr">
+      <c r="W95" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U95" s="5" t="inlineStr">
+      <c r="X95" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V95" s="5" t="inlineStr">
+      <c r="Y95" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -9404,38 +10151,41 @@
           <t>Resolución exenta 60 de fecha 16/01/2019</t>
         </is>
       </c>
-      <c r="O96" s="12" t="inlineStr">
+      <c r="O96" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P96" s="7" t="inlineStr">
+      <c r="P96" s="8" t="inlineStr"/>
+      <c r="Q96" s="8" t="inlineStr"/>
+      <c r="R96" s="8" t="inlineStr"/>
+      <c r="S96" s="7" t="inlineStr">
         <is>
           <t>colegioossandon.cl</t>
         </is>
       </c>
-      <c r="Q96" s="8" t="inlineStr">
+      <c r="T96" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Lihuen</t>
         </is>
       </c>
-      <c r="R96" s="7" t="n">
+      <c r="U96" s="7" t="n">
         <v>-29.964579</v>
       </c>
-      <c r="S96" s="7" t="n">
+      <c r="V96" s="7" t="n">
         <v>-71.345381</v>
       </c>
-      <c r="T96" s="8" t="inlineStr">
+      <c r="W96" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U96" s="8" t="inlineStr">
+      <c r="X96" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V96" s="8" t="inlineStr"/>
+      <c r="Y96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -9507,29 +10257,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P97" s="4" t="inlineStr"/>
-      <c r="Q97" s="5" t="inlineStr">
+      <c r="P97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="inlineStr"/>
+      <c r="R97" s="5" t="inlineStr"/>
+      <c r="S97" s="4" t="inlineStr"/>
+      <c r="T97" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Escuela Especial Cordillera Sindempart</t>
         </is>
       </c>
-      <c r="R97" s="4" t="n">
+      <c r="U97" s="4" t="n">
         <v>-29.97955</v>
       </c>
-      <c r="S97" s="4" t="n">
+      <c r="V97" s="4" t="n">
         <v>-71.33862999999999</v>
       </c>
-      <c r="T97" s="5" t="inlineStr">
+      <c r="W97" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U97" s="5" t="inlineStr">
+      <c r="X97" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V97" s="5" t="inlineStr"/>
+      <c r="Y97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -9601,33 +10354,36 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P98" s="7" t="inlineStr">
+      <c r="P98" s="8" t="inlineStr"/>
+      <c r="Q98" s="8" t="inlineStr"/>
+      <c r="R98" s="8" t="inlineStr"/>
+      <c r="S98" s="7" t="inlineStr">
         <is>
           <t>www.escuelahispanoamericana.cl</t>
         </is>
       </c>
-      <c r="Q98" s="8" t="inlineStr">
+      <c r="T98" s="8" t="inlineStr">
         <is>
           <t>Escuela De Lenguaje Hispanoamericana Corporación Educacional</t>
         </is>
       </c>
-      <c r="R98" s="7" t="n">
+      <c r="U98" s="7" t="n">
         <v>-29.977905</v>
       </c>
-      <c r="S98" s="7" t="n">
+      <c r="V98" s="7" t="n">
         <v>-71.32853</v>
       </c>
-      <c r="T98" s="8" t="inlineStr">
+      <c r="W98" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U98" s="8" t="inlineStr">
+      <c r="X98" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V98" s="8" t="inlineStr"/>
+      <c r="Y98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -9699,29 +10455,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P99" s="4" t="inlineStr"/>
-      <c r="Q99" s="5" t="inlineStr">
+      <c r="P99" s="5" t="inlineStr"/>
+      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="R99" s="5" t="inlineStr"/>
+      <c r="S99" s="4" t="inlineStr"/>
+      <c r="T99" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Escuela Especial Cordillera Porvenir</t>
         </is>
       </c>
-      <c r="R99" s="4" t="n">
+      <c r="U99" s="4" t="n">
         <v>-29.969617</v>
       </c>
-      <c r="S99" s="4" t="n">
+      <c r="V99" s="4" t="n">
         <v>-71.304102</v>
       </c>
-      <c r="T99" s="5" t="inlineStr">
+      <c r="W99" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U99" s="5" t="inlineStr">
+      <c r="X99" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V99" s="5" t="inlineStr">
+      <c r="Y99" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -9797,29 +10556,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P100" s="7" t="inlineStr"/>
-      <c r="Q100" s="8" t="inlineStr">
+      <c r="P100" s="8" t="inlineStr"/>
+      <c r="Q100" s="8" t="inlineStr"/>
+      <c r="R100" s="8" t="inlineStr"/>
+      <c r="S100" s="7" t="inlineStr"/>
+      <c r="T100" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Perspectiva</t>
         </is>
       </c>
-      <c r="R100" s="7" t="n">
+      <c r="U100" s="7" t="n">
         <v>-29.946777</v>
       </c>
-      <c r="S100" s="7" t="n">
+      <c r="V100" s="7" t="n">
         <v>-71.35122</v>
       </c>
-      <c r="T100" s="8" t="inlineStr">
+      <c r="W100" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U100" s="8" t="inlineStr">
+      <c r="X100" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V100" s="8" t="inlineStr"/>
+      <c r="Y100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -9891,29 +10653,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P101" s="4" t="inlineStr"/>
-      <c r="Q101" s="5" t="inlineStr">
+      <c r="P101" s="5" t="inlineStr"/>
+      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="R101" s="5" t="inlineStr"/>
+      <c r="S101" s="4" t="inlineStr"/>
+      <c r="T101" s="5" t="inlineStr">
         <is>
           <t>José Marti Corporacion Educacional</t>
         </is>
       </c>
-      <c r="R101" s="4" t="n">
+      <c r="U101" s="4" t="n">
         <v>-29.972258</v>
       </c>
-      <c r="S101" s="4" t="n">
+      <c r="V101" s="4" t="n">
         <v>-71.329155</v>
       </c>
-      <c r="T101" s="5" t="inlineStr">
+      <c r="W101" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U101" s="5" t="inlineStr">
+      <c r="X101" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V101" s="5" t="inlineStr"/>
+      <c r="Y101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -9985,29 +10750,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P102" s="7" t="inlineStr">
+      <c r="P102" s="8" t="inlineStr"/>
+      <c r="Q102" s="8" t="inlineStr"/>
+      <c r="R102" s="8" t="inlineStr"/>
+      <c r="S102" s="7" t="inlineStr">
         <is>
           <t>www.escueladelenguajesancarlos.cl</t>
         </is>
       </c>
-      <c r="Q102" s="8" t="inlineStr">
+      <c r="T102" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional San Carlos Del Bosque</t>
         </is>
       </c>
-      <c r="R102" s="7" t="n">
+      <c r="U102" s="7" t="n">
         <v>-29.973524</v>
       </c>
-      <c r="S102" s="7" t="n">
+      <c r="V102" s="7" t="n">
         <v>-71.25271600000001</v>
       </c>
-      <c r="T102" s="8" t="inlineStr">
+      <c r="W102" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U102" s="8" t="inlineStr"/>
-      <c r="V102" s="8" t="inlineStr"/>
+      <c r="X102" s="8" t="inlineStr"/>
+      <c r="Y102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -10059,12 +10827,12 @@
           <t>Valle De Elqui 103, Tongoy</t>
         </is>
       </c>
-      <c r="L103" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M103" s="13" t="inlineStr">
+      <c r="L103" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -10079,25 +10847,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P103" s="4" t="inlineStr"/>
-      <c r="Q103" s="5" t="inlineStr">
+      <c r="P103" s="5" t="inlineStr"/>
+      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="R103" s="5" t="inlineStr"/>
+      <c r="S103" s="4" t="inlineStr"/>
+      <c r="T103" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Horizonte De Palabras</t>
         </is>
       </c>
-      <c r="R103" s="4" t="n">
+      <c r="U103" s="4" t="n">
         <v>-30.259869</v>
       </c>
-      <c r="S103" s="4" t="n">
+      <c r="V103" s="4" t="n">
         <v>-71.49301</v>
       </c>
-      <c r="T103" s="5" t="inlineStr">
+      <c r="W103" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U103" s="5" t="inlineStr"/>
-      <c r="V103" s="5" t="inlineStr"/>
+      <c r="X103" s="5" t="inlineStr"/>
+      <c r="Y103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -10169,33 +10940,36 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P104" s="7" t="inlineStr">
+      <c r="P104" s="8" t="inlineStr"/>
+      <c r="Q104" s="8" t="inlineStr"/>
+      <c r="R104" s="8" t="inlineStr"/>
+      <c r="S104" s="7" t="inlineStr">
         <is>
           <t>www.cedin.cl</t>
         </is>
       </c>
-      <c r="Q104" s="8" t="inlineStr">
+      <c r="T104" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Centro De Estudios Y Desarrollo Integral Del Niño</t>
         </is>
       </c>
-      <c r="R104" s="7" t="n">
+      <c r="U104" s="7" t="n">
         <v>-29.957296</v>
       </c>
-      <c r="S104" s="7" t="n">
+      <c r="V104" s="7" t="n">
         <v>-71.24834</v>
       </c>
-      <c r="T104" s="8" t="inlineStr">
+      <c r="W104" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U104" s="8" t="inlineStr">
+      <c r="X104" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V104" s="8" t="inlineStr"/>
+      <c r="Y104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -10247,12 +11021,12 @@
           <t>Pasaje Interior Los Olivos 851</t>
         </is>
       </c>
-      <c r="L105" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M105" s="13" t="inlineStr">
+      <c r="L105" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M105" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -10267,25 +11041,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P105" s="4" t="inlineStr"/>
-      <c r="Q105" s="5" t="inlineStr">
+      <c r="P105" s="5" t="inlineStr"/>
+      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="R105" s="5" t="inlineStr"/>
+      <c r="S105" s="4" t="inlineStr"/>
+      <c r="T105" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional   Wenui</t>
         </is>
       </c>
-      <c r="R105" s="4" t="n">
+      <c r="U105" s="4" t="n">
         <v>-29.99611</v>
       </c>
-      <c r="S105" s="4" t="n">
+      <c r="V105" s="4" t="n">
         <v>-71.337605</v>
       </c>
-      <c r="T105" s="5" t="inlineStr">
+      <c r="W105" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U105" s="5" t="inlineStr"/>
-      <c r="V105" s="5" t="inlineStr">
+      <c r="X105" s="5" t="inlineStr"/>
+      <c r="Y105" s="5" t="inlineStr">
         <is>
           <t>Número con formato irregular: verificar</t>
         </is>
@@ -10361,29 +11138,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P106" s="7" t="inlineStr"/>
-      <c r="Q106" s="8" t="inlineStr">
+      <c r="P106" s="8" t="inlineStr"/>
+      <c r="Q106" s="8" t="inlineStr"/>
+      <c r="R106" s="8" t="inlineStr"/>
+      <c r="S106" s="7" t="inlineStr"/>
+      <c r="T106" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Alegría</t>
         </is>
       </c>
-      <c r="R106" s="7" t="n">
+      <c r="U106" s="7" t="n">
         <v>-29.95661</v>
       </c>
-      <c r="S106" s="7" t="n">
+      <c r="V106" s="7" t="n">
         <v>-71.34820000000001</v>
       </c>
-      <c r="T106" s="8" t="inlineStr">
+      <c r="W106" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U106" s="8" t="inlineStr">
+      <c r="X106" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V106" s="8" t="inlineStr">
+      <c r="Y106" s="8" t="inlineStr">
         <is>
           <t>Prefijo de Santiago: verificar</t>
         </is>
@@ -10459,29 +11239,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P107" s="4" t="inlineStr"/>
-      <c r="Q107" s="5" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr"/>
+      <c r="Q107" s="5" t="inlineStr"/>
+      <c r="R107" s="5" t="inlineStr"/>
+      <c r="S107" s="4" t="inlineStr"/>
+      <c r="T107" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Valdani</t>
         </is>
       </c>
-      <c r="R107" s="4" t="n">
+      <c r="U107" s="4" t="n">
         <v>-29.98450661</v>
       </c>
-      <c r="S107" s="4" t="n">
+      <c r="V107" s="4" t="n">
         <v>-71.34375</v>
       </c>
-      <c r="T107" s="5" t="inlineStr">
+      <c r="W107" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U107" s="5" t="inlineStr">
+      <c r="X107" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V107" s="5" t="inlineStr"/>
+      <c r="Y107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -10553,29 +11336,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P108" s="7" t="inlineStr"/>
-      <c r="Q108" s="8" t="inlineStr">
+      <c r="P108" s="8" t="inlineStr"/>
+      <c r="Q108" s="8" t="inlineStr"/>
+      <c r="R108" s="8" t="inlineStr"/>
+      <c r="S108" s="7" t="inlineStr"/>
+      <c r="T108" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Diego Rivera</t>
         </is>
       </c>
-      <c r="R108" s="7" t="n">
+      <c r="U108" s="7" t="n">
         <v>-29.96583748</v>
       </c>
-      <c r="S108" s="7" t="n">
+      <c r="V108" s="7" t="n">
         <v>-71.26084136999999</v>
       </c>
-      <c r="T108" s="8" t="inlineStr">
+      <c r="W108" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U108" s="8" t="inlineStr">
+      <c r="X108" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V108" s="8" t="inlineStr"/>
+      <c r="Y108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -10642,38 +11428,41 @@
           <t>Resolución exenta 1534 de fecha 12/07/2017</t>
         </is>
       </c>
-      <c r="O109" s="12" t="inlineStr">
+      <c r="O109" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P109" s="4" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr"/>
+      <c r="Q109" s="5" t="inlineStr"/>
+      <c r="R109" s="5" t="inlineStr"/>
+      <c r="S109" s="4" t="inlineStr">
         <is>
           <t>www.diegodealmeyda.cl</t>
         </is>
       </c>
-      <c r="Q109" s="5" t="inlineStr">
+      <c r="T109" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Diego De Almeyda</t>
         </is>
       </c>
-      <c r="R109" s="4" t="n">
+      <c r="U109" s="4" t="n">
         <v>-29.95982</v>
       </c>
-      <c r="S109" s="4" t="n">
+      <c r="V109" s="4" t="n">
         <v>-71.250908</v>
       </c>
-      <c r="T109" s="5" t="inlineStr">
+      <c r="W109" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U109" s="5" t="inlineStr">
+      <c r="X109" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V109" s="5" t="inlineStr"/>
+      <c r="Y109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -10745,29 +11534,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P110" s="7" t="inlineStr">
+      <c r="P110" s="8" t="inlineStr"/>
+      <c r="Q110" s="8" t="inlineStr"/>
+      <c r="R110" s="8" t="inlineStr"/>
+      <c r="S110" s="7" t="inlineStr">
         <is>
           <t>www.escuelaentremundos.com</t>
         </is>
       </c>
-      <c r="Q110" s="8" t="inlineStr">
+      <c r="T110" s="8" t="inlineStr">
         <is>
           <t>Fundación Educacional Comenzar</t>
         </is>
       </c>
-      <c r="R110" s="7" t="n">
+      <c r="U110" s="7" t="n">
         <v>-29.97814</v>
       </c>
-      <c r="S110" s="7" t="n">
+      <c r="V110" s="7" t="n">
         <v>-71.340324</v>
       </c>
-      <c r="T110" s="8" t="inlineStr">
+      <c r="W110" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U110" s="8" t="inlineStr"/>
-      <c r="V110" s="8" t="inlineStr"/>
+      <c r="X110" s="8" t="inlineStr"/>
+      <c r="Y110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -10839,29 +11631,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P111" s="4" t="inlineStr"/>
-      <c r="Q111" s="5" t="inlineStr">
+      <c r="P111" s="5" t="inlineStr"/>
+      <c r="Q111" s="5" t="inlineStr"/>
+      <c r="R111" s="5" t="inlineStr"/>
+      <c r="S111" s="4" t="inlineStr"/>
+      <c r="T111" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Escuela Especial Cordillera Parte Alta</t>
         </is>
       </c>
-      <c r="R111" s="4" t="n">
+      <c r="U111" s="4" t="n">
         <v>-29.944397</v>
       </c>
-      <c r="S111" s="4" t="n">
+      <c r="V111" s="4" t="n">
         <v>-71.33898000000001</v>
       </c>
-      <c r="T111" s="5" t="inlineStr">
+      <c r="W111" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U111" s="5" t="inlineStr">
+      <c r="X111" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V111" s="5" t="inlineStr">
+      <c r="Y111" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -10937,29 +11732,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P112" s="7" t="inlineStr"/>
-      <c r="Q112" s="8" t="inlineStr">
+      <c r="P112" s="8" t="inlineStr"/>
+      <c r="Q112" s="8" t="inlineStr"/>
+      <c r="R112" s="8" t="inlineStr"/>
+      <c r="S112" s="7" t="inlineStr"/>
+      <c r="T112" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional  Capacidades Diferentes</t>
         </is>
       </c>
-      <c r="R112" s="7" t="n">
+      <c r="U112" s="7" t="n">
         <v>-29.957686</v>
       </c>
-      <c r="S112" s="7" t="n">
+      <c r="V112" s="7" t="n">
         <v>-71.343143</v>
       </c>
-      <c r="T112" s="8" t="inlineStr">
+      <c r="W112" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U112" s="8" t="inlineStr">
+      <c r="X112" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC) (la corporación Unpade nació el 7 de julio de 1986)</t>
         </is>
       </c>
-      <c r="V112" s="8" t="inlineStr"/>
+      <c r="Y112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -11011,12 +11809,12 @@
           <t>Javiera Carrera 5</t>
         </is>
       </c>
-      <c r="L113" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M113" s="13" t="inlineStr">
+      <c r="L113" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M113" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11031,25 +11829,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P113" s="4" t="inlineStr"/>
-      <c r="Q113" s="5" t="inlineStr">
+      <c r="P113" s="5" t="inlineStr"/>
+      <c r="Q113" s="5" t="inlineStr"/>
+      <c r="R113" s="5" t="inlineStr"/>
+      <c r="S113" s="4" t="inlineStr"/>
+      <c r="T113" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Padre Alberto Hurtado</t>
         </is>
       </c>
-      <c r="R113" s="4" t="n">
+      <c r="U113" s="4" t="n">
         <v>-29.980446</v>
       </c>
-      <c r="S113" s="4" t="n">
+      <c r="V113" s="4" t="n">
         <v>-71.25884000000001</v>
       </c>
-      <c r="T113" s="5" t="inlineStr">
+      <c r="W113" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U113" s="5" t="inlineStr"/>
-      <c r="V113" s="5" t="inlineStr"/>
+      <c r="X113" s="5" t="inlineStr"/>
+      <c r="Y113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -11121,29 +11922,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P114" s="7" t="inlineStr">
+      <c r="P114" s="8" t="inlineStr"/>
+      <c r="Q114" s="8" t="inlineStr"/>
+      <c r="R114" s="8" t="inlineStr"/>
+      <c r="S114" s="7" t="inlineStr">
         <is>
           <t>www.paxterra.cl</t>
         </is>
       </c>
-      <c r="Q114" s="8" t="inlineStr">
+      <c r="T114" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Pax Terra</t>
         </is>
       </c>
-      <c r="R114" s="7" t="n">
+      <c r="U114" s="7" t="n">
         <v>-29.964972</v>
       </c>
-      <c r="S114" s="7" t="n">
+      <c r="V114" s="7" t="n">
         <v>-71.248983</v>
       </c>
-      <c r="T114" s="8" t="inlineStr">
+      <c r="W114" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U114" s="8" t="inlineStr"/>
-      <c r="V114" s="8" t="inlineStr"/>
+      <c r="X114" s="8" t="inlineStr"/>
+      <c r="Y114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -11195,7 +11999,7 @@
           <t>Escuela Especial De Lenguaje Arcoíris De Palabras, Ubicado En Pasaje Luis Campos Maluenda N° 377, H. Oriente, Sector Urbano, De La Comuna De Coquimbo 377</t>
         </is>
       </c>
-      <c r="L115" s="14" t="inlineStr">
+      <c r="L115" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11215,29 +12019,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P115" s="4" t="inlineStr"/>
-      <c r="Q115" s="5" t="inlineStr">
+      <c r="P115" s="5" t="inlineStr"/>
+      <c r="Q115" s="5" t="inlineStr"/>
+      <c r="R115" s="5" t="inlineStr"/>
+      <c r="S115" s="4" t="inlineStr"/>
+      <c r="T115" s="5" t="inlineStr">
         <is>
           <t>Anisi Entidad Individual Educacional</t>
         </is>
       </c>
-      <c r="R115" s="4" t="n">
+      <c r="U115" s="4" t="n">
         <v>-29.983994</v>
       </c>
-      <c r="S115" s="4" t="n">
+      <c r="V115" s="4" t="n">
         <v>-71.33664400000001</v>
       </c>
-      <c r="T115" s="5" t="inlineStr">
+      <c r="W115" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U115" s="5" t="inlineStr">
+      <c r="X115" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V115" s="5" t="inlineStr">
+      <c r="Y115" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -11313,25 +12120,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P116" s="7" t="inlineStr"/>
-      <c r="Q116" s="8" t="inlineStr">
+      <c r="P116" s="8" t="inlineStr"/>
+      <c r="Q116" s="8" t="inlineStr"/>
+      <c r="R116" s="8" t="inlineStr"/>
+      <c r="S116" s="7" t="inlineStr"/>
+      <c r="T116" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Kreamundos</t>
         </is>
       </c>
-      <c r="R116" s="7" t="n">
+      <c r="U116" s="7" t="n">
         <v>-29.95969</v>
       </c>
-      <c r="S116" s="7" t="n">
+      <c r="V116" s="7" t="n">
         <v>-71.26006</v>
       </c>
-      <c r="T116" s="8" t="inlineStr">
+      <c r="W116" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U116" s="8" t="inlineStr"/>
-      <c r="V116" s="8" t="inlineStr"/>
+      <c r="X116" s="8" t="inlineStr"/>
+      <c r="Y116" s="8" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -11368,7 +12178,7 @@
           <t>Carolina Judith Lazo Barahona</t>
         </is>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I117" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11383,12 +12193,12 @@
           <t>Los Clarines 1763 Herradura Oriente</t>
         </is>
       </c>
-      <c r="L117" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M117" s="13" t="inlineStr">
+      <c r="L117" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11403,29 +12213,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P117" s="4" t="inlineStr">
+      <c r="P117" s="5" t="inlineStr"/>
+      <c r="Q117" s="5" t="inlineStr"/>
+      <c r="R117" s="5" t="inlineStr"/>
+      <c r="S117" s="4" t="inlineStr">
         <is>
           <t>www.entretepalabras.cl</t>
         </is>
       </c>
-      <c r="Q117" s="5" t="inlineStr">
+      <c r="T117" s="5" t="inlineStr">
         <is>
           <t>Entretepalabras C.e.</t>
         </is>
       </c>
-      <c r="R117" s="4" t="n">
+      <c r="U117" s="4" t="n">
         <v>-29.969055</v>
       </c>
-      <c r="S117" s="4" t="n">
+      <c r="V117" s="4" t="n">
         <v>-71.24937</v>
       </c>
-      <c r="T117" s="5" t="inlineStr">
+      <c r="W117" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U117" s="5" t="inlineStr"/>
-      <c r="V117" s="5" t="inlineStr"/>
+      <c r="X117" s="5" t="inlineStr"/>
+      <c r="Y117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
@@ -11497,29 +12310,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P118" s="7" t="inlineStr"/>
-      <c r="Q118" s="8" t="inlineStr">
+      <c r="P118" s="8" t="inlineStr"/>
+      <c r="Q118" s="8" t="inlineStr"/>
+      <c r="R118" s="8" t="inlineStr"/>
+      <c r="S118" s="7" t="inlineStr"/>
+      <c r="T118" s="8" t="inlineStr">
         <is>
           <t>Escuela Especial De Trastornos Del Lenguaje Hamelin Corporación Educacional</t>
         </is>
       </c>
-      <c r="R118" s="7" t="n">
+      <c r="U118" s="7" t="n">
         <v>-29.99129</v>
       </c>
-      <c r="S118" s="7" t="n">
+      <c r="V118" s="7" t="n">
         <v>-71.32441</v>
       </c>
-      <c r="T118" s="8" t="inlineStr">
+      <c r="W118" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U118" s="8" t="inlineStr">
+      <c r="X118" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V118" s="8" t="inlineStr">
+      <c r="Y118" s="8" t="inlineStr">
         <is>
           <t>Número con formato irregular: verificar</t>
         </is>
@@ -11575,7 +12391,7 @@
           <t>Avenida Portugal Loteo Punta Mira Norte 2710</t>
         </is>
       </c>
-      <c r="L119" s="14" t="inlineStr">
+      <c r="L119" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11595,29 +12411,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P119" s="4" t="inlineStr"/>
-      <c r="Q119" s="5" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr"/>
+      <c r="Q119" s="5" t="inlineStr"/>
+      <c r="R119" s="5" t="inlineStr"/>
+      <c r="S119" s="4" t="inlineStr"/>
+      <c r="T119" s="5" t="inlineStr">
         <is>
           <t>Inti E.i.e.</t>
         </is>
       </c>
-      <c r="R119" s="4" t="n">
+      <c r="U119" s="4" t="n">
         <v>-29.99396</v>
       </c>
-      <c r="S119" s="4" t="n">
+      <c r="V119" s="4" t="n">
         <v>-71.32635999999999</v>
       </c>
-      <c r="T119" s="5" t="inlineStr">
+      <c r="W119" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U119" s="5" t="inlineStr">
+      <c r="X119" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V119" s="5" t="inlineStr"/>
+      <c r="Y119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -11689,29 +12508,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P120" s="7" t="inlineStr"/>
-      <c r="Q120" s="8" t="inlineStr">
+      <c r="P120" s="8" t="inlineStr"/>
+      <c r="Q120" s="8" t="inlineStr"/>
+      <c r="R120" s="8" t="inlineStr"/>
+      <c r="S120" s="7" t="inlineStr"/>
+      <c r="T120" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional San Sebastian  De Coquimbo</t>
         </is>
       </c>
-      <c r="R120" s="7" t="n">
+      <c r="U120" s="7" t="n">
         <v>-29.96708</v>
       </c>
-      <c r="S120" s="7" t="n">
+      <c r="V120" s="7" t="n">
         <v>-71.34772</v>
       </c>
-      <c r="T120" s="8" t="inlineStr">
+      <c r="W120" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U120" s="8" t="inlineStr">
+      <c r="X120" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V120" s="8" t="inlineStr"/>
+      <c r="Y120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -11763,12 +12585,12 @@
           <t>Jose Santos Ossa 18</t>
         </is>
       </c>
-      <c r="L121" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M121" s="13" t="inlineStr">
+      <c r="L121" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -11783,25 +12605,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P121" s="4" t="inlineStr"/>
-      <c r="Q121" s="5" t="inlineStr">
+      <c r="P121" s="5" t="inlineStr"/>
+      <c r="Q121" s="5" t="inlineStr"/>
+      <c r="R121" s="5" t="inlineStr"/>
+      <c r="S121" s="4" t="inlineStr"/>
+      <c r="T121" s="5" t="inlineStr">
         <is>
           <t>Tierra De Ángeles Entidad Individual De Educación</t>
         </is>
       </c>
-      <c r="R121" s="4" t="n">
+      <c r="U121" s="4" t="n">
         <v>-29.97809</v>
       </c>
-      <c r="S121" s="4" t="n">
+      <c r="V121" s="4" t="n">
         <v>-71.24852</v>
       </c>
-      <c r="T121" s="5" t="inlineStr">
+      <c r="W121" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U121" s="5" t="inlineStr"/>
-      <c r="V121" s="5" t="inlineStr"/>
+      <c r="X121" s="5" t="inlineStr"/>
+      <c r="Y121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
@@ -11873,29 +12698,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P122" s="7" t="inlineStr">
+      <c r="P122" s="8" t="inlineStr"/>
+      <c r="Q122" s="8" t="inlineStr"/>
+      <c r="R122" s="8" t="inlineStr"/>
+      <c r="S122" s="7" t="inlineStr">
         <is>
           <t>www.escuelaarbol.cl</t>
         </is>
       </c>
-      <c r="Q122" s="8" t="inlineStr">
+      <c r="T122" s="8" t="inlineStr">
         <is>
           <t>Giannini Tomic Entidad Individual Educacional</t>
         </is>
       </c>
-      <c r="R122" s="7" t="n">
+      <c r="U122" s="7" t="n">
         <v>-29.962047</v>
       </c>
-      <c r="S122" s="7" t="n">
+      <c r="V122" s="7" t="n">
         <v>-71.300422</v>
       </c>
-      <c r="T122" s="8" t="inlineStr">
+      <c r="W122" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U122" s="8" t="inlineStr"/>
-      <c r="V122" s="8" t="inlineStr">
+      <c r="X122" s="8" t="inlineStr"/>
+      <c r="Y122" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -11971,29 +12799,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P123" s="4" t="inlineStr"/>
-      <c r="Q123" s="5" t="inlineStr">
+      <c r="P123" s="5" t="inlineStr"/>
+      <c r="Q123" s="5" t="inlineStr"/>
+      <c r="R123" s="5" t="inlineStr"/>
+      <c r="S123" s="4" t="inlineStr"/>
+      <c r="T123" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional La Tríada</t>
         </is>
       </c>
-      <c r="R123" s="4" t="n">
+      <c r="U123" s="4" t="n">
         <v>-30.007382</v>
       </c>
-      <c r="S123" s="4" t="n">
+      <c r="V123" s="4" t="n">
         <v>-71.329643</v>
       </c>
-      <c r="T123" s="5" t="inlineStr">
+      <c r="W123" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U123" s="5" t="inlineStr">
+      <c r="X123" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V123" s="5" t="inlineStr">
+      <c r="Y123" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -12069,25 +12900,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P124" s="7" t="inlineStr"/>
-      <c r="Q124" s="8" t="inlineStr">
+      <c r="P124" s="8" t="inlineStr"/>
+      <c r="Q124" s="8" t="inlineStr"/>
+      <c r="R124" s="8" t="inlineStr"/>
+      <c r="S124" s="7" t="inlineStr"/>
+      <c r="T124" s="8" t="inlineStr">
         <is>
           <t>Corporacion Educacional Munay</t>
         </is>
       </c>
-      <c r="R124" s="7" t="n">
+      <c r="U124" s="7" t="n">
         <v>-29.962547</v>
       </c>
-      <c r="S124" s="7" t="n">
+      <c r="V124" s="7" t="n">
         <v>-71.33750000000001</v>
       </c>
-      <c r="T124" s="8" t="inlineStr">
+      <c r="W124" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U124" s="8" t="inlineStr"/>
-      <c r="V124" s="8" t="inlineStr">
+      <c r="X124" s="8" t="inlineStr"/>
+      <c r="Y124" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -12143,12 +12977,12 @@
           <t>Santiago Amengual 22</t>
         </is>
       </c>
-      <c r="L125" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M125" s="13" t="inlineStr">
+      <c r="L125" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -12163,25 +12997,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P125" s="4" t="inlineStr"/>
-      <c r="Q125" s="5" t="inlineStr">
+      <c r="P125" s="5" t="inlineStr"/>
+      <c r="Q125" s="5" t="inlineStr"/>
+      <c r="R125" s="5" t="inlineStr"/>
+      <c r="S125" s="4" t="inlineStr"/>
+      <c r="T125" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Sueños</t>
         </is>
       </c>
-      <c r="R125" s="4" t="n">
+      <c r="U125" s="4" t="n">
         <v>-29.97292</v>
       </c>
-      <c r="S125" s="4" t="n">
+      <c r="V125" s="4" t="n">
         <v>-71.3295</v>
       </c>
-      <c r="T125" s="5" t="inlineStr">
+      <c r="W125" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U125" s="5" t="inlineStr"/>
-      <c r="V125" s="5" t="inlineStr">
+      <c r="X125" s="5" t="inlineStr"/>
+      <c r="Y125" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -12257,25 +13094,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P126" s="7" t="inlineStr"/>
-      <c r="Q126" s="8" t="inlineStr">
+      <c r="P126" s="8" t="inlineStr"/>
+      <c r="Q126" s="8" t="inlineStr"/>
+      <c r="R126" s="8" t="inlineStr"/>
+      <c r="S126" s="7" t="inlineStr"/>
+      <c r="T126" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional   Bordemar</t>
         </is>
       </c>
-      <c r="R126" s="7" t="n">
+      <c r="U126" s="7" t="n">
         <v>-29.98132</v>
       </c>
-      <c r="S126" s="7" t="n">
+      <c r="V126" s="7" t="n">
         <v>-71.29749</v>
       </c>
-      <c r="T126" s="8" t="inlineStr">
+      <c r="W126" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U126" s="8" t="inlineStr"/>
-      <c r="V126" s="8" t="inlineStr">
+      <c r="X126" s="8" t="inlineStr"/>
+      <c r="Y126" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -12331,12 +13171,12 @@
           <t>Tarapaca 1020 1020</t>
         </is>
       </c>
-      <c r="L127" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M127" s="13" t="inlineStr">
+      <c r="L127" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -12351,25 +13191,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P127" s="4" t="inlineStr"/>
-      <c r="Q127" s="5" t="inlineStr">
+      <c r="P127" s="5" t="inlineStr"/>
+      <c r="Q127" s="5" t="inlineStr"/>
+      <c r="R127" s="5" t="inlineStr"/>
+      <c r="S127" s="4" t="inlineStr"/>
+      <c r="T127" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional El Sendero</t>
         </is>
       </c>
-      <c r="R127" s="4" t="n">
+      <c r="U127" s="4" t="n">
         <v>-29.958744</v>
       </c>
-      <c r="S127" s="4" t="n">
+      <c r="V127" s="4" t="n">
         <v>-71.25819</v>
       </c>
-      <c r="T127" s="5" t="inlineStr">
+      <c r="W127" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U127" s="5" t="inlineStr"/>
-      <c r="V127" s="5" t="inlineStr">
+      <c r="X127" s="5" t="inlineStr"/>
+      <c r="Y127" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -12445,25 +13288,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P128" s="7" t="inlineStr"/>
-      <c r="Q128" s="8" t="inlineStr">
+      <c r="P128" s="8" t="inlineStr"/>
+      <c r="Q128" s="8" t="inlineStr"/>
+      <c r="R128" s="8" t="inlineStr"/>
+      <c r="S128" s="7" t="inlineStr"/>
+      <c r="T128" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional  Cumbre De Palabras La Serena</t>
         </is>
       </c>
-      <c r="R128" s="7" t="n">
+      <c r="U128" s="7" t="n">
         <v>-29.97958</v>
       </c>
-      <c r="S128" s="7" t="n">
+      <c r="V128" s="7" t="n">
         <v>-71.30059</v>
       </c>
-      <c r="T128" s="8" t="inlineStr">
+      <c r="W128" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U128" s="8" t="inlineStr"/>
-      <c r="V128" s="8" t="inlineStr"/>
+      <c r="X128" s="8" t="inlineStr"/>
+      <c r="Y128" s="8" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -12515,12 +13361,12 @@
           <t>Esmeralda 1105</t>
         </is>
       </c>
-      <c r="L129" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M129" s="13" t="inlineStr">
+      <c r="L129" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -12535,25 +13381,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P129" s="4" t="inlineStr"/>
-      <c r="Q129" s="5" t="inlineStr">
+      <c r="P129" s="5" t="inlineStr"/>
+      <c r="Q129" s="5" t="inlineStr"/>
+      <c r="R129" s="5" t="inlineStr"/>
+      <c r="S129" s="4" t="inlineStr"/>
+      <c r="T129" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Padre Alberto Hurtado</t>
         </is>
       </c>
-      <c r="R129" s="4" t="n">
+      <c r="U129" s="4" t="n">
         <v>-29.954714</v>
       </c>
-      <c r="S129" s="4" t="n">
+      <c r="V129" s="4" t="n">
         <v>-71.34878500000001</v>
       </c>
-      <c r="T129" s="5" t="inlineStr">
+      <c r="W129" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U129" s="5" t="inlineStr"/>
-      <c r="V129" s="5" t="inlineStr"/>
+      <c r="X129" s="5" t="inlineStr"/>
+      <c r="Y129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -12625,33 +13474,36 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P130" s="7" t="inlineStr">
+      <c r="P130" s="8" t="inlineStr"/>
+      <c r="Q130" s="8" t="inlineStr"/>
+      <c r="R130" s="8" t="inlineStr"/>
+      <c r="S130" s="7" t="inlineStr">
         <is>
           <t>www.escueladelenguajeelsauce.cl</t>
         </is>
       </c>
-      <c r="Q130" s="8" t="inlineStr">
+      <c r="T130" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional El Sauce Coquimbo</t>
         </is>
       </c>
-      <c r="R130" s="7" t="n">
+      <c r="U130" s="7" t="n">
         <v>-29.99727</v>
       </c>
-      <c r="S130" s="7" t="n">
+      <c r="V130" s="7" t="n">
         <v>-71.33699</v>
       </c>
-      <c r="T130" s="8" t="inlineStr">
+      <c r="W130" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U130" s="8" t="inlineStr">
+      <c r="X130" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V130" s="8" t="inlineStr"/>
+      <c r="Y130" s="8" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -12703,12 +13555,12 @@
           <t>Tomas Veliz Castillo 785</t>
         </is>
       </c>
-      <c r="L131" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M131" s="13" t="inlineStr">
+      <c r="L131" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -12718,34 +13570,37 @@
           <t>Resolución exenta 910 de fecha 26/03/2004</t>
         </is>
       </c>
-      <c r="O131" s="12" t="inlineStr">
+      <c r="O131" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P131" s="4" t="inlineStr">
+      <c r="P131" s="5" t="inlineStr"/>
+      <c r="Q131" s="5" t="inlineStr"/>
+      <c r="R131" s="5" t="inlineStr"/>
+      <c r="S131" s="4" t="inlineStr">
         <is>
           <t>sites.google.com/latinoamericaeduca.cl/lae</t>
         </is>
       </c>
-      <c r="Q131" s="5" t="inlineStr">
+      <c r="T131" s="5" t="inlineStr">
         <is>
           <t>Corporación Latinoamérica Educa</t>
         </is>
       </c>
-      <c r="R131" s="4" t="n">
+      <c r="U131" s="4" t="n">
         <v>-29.996759</v>
       </c>
-      <c r="S131" s="4" t="n">
+      <c r="V131" s="4" t="n">
         <v>-71.327881</v>
       </c>
-      <c r="T131" s="5" t="inlineStr">
+      <c r="W131" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U131" s="5" t="inlineStr"/>
-      <c r="V131" s="5" t="inlineStr"/>
+      <c r="X131" s="5" t="inlineStr"/>
+      <c r="Y131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
@@ -12812,30 +13667,33 @@
           <t>Resolución exenta 1908 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O132" s="12" t="inlineStr">
+      <c r="O132" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P132" s="7" t="inlineStr"/>
-      <c r="Q132" s="8" t="inlineStr">
+      <c r="P132" s="8" t="inlineStr"/>
+      <c r="Q132" s="8" t="inlineStr"/>
+      <c r="R132" s="8" t="inlineStr"/>
+      <c r="S132" s="7" t="inlineStr"/>
+      <c r="T132" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional  Graciela Judith</t>
         </is>
       </c>
-      <c r="R132" s="7" t="n">
+      <c r="U132" s="7" t="n">
         <v>-29.954094</v>
       </c>
-      <c r="S132" s="7" t="n">
+      <c r="V132" s="7" t="n">
         <v>-71.27204999999999</v>
       </c>
-      <c r="T132" s="8" t="inlineStr">
+      <c r="W132" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U132" s="8" t="inlineStr"/>
-      <c r="V132" s="8" t="inlineStr"/>
+      <c r="X132" s="8" t="inlineStr"/>
+      <c r="Y132" s="8" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -12902,38 +13760,41 @@
           <t>Resolución exenta 1777 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O133" s="12" t="inlineStr">
+      <c r="O133" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P133" s="4" t="inlineStr">
+      <c r="P133" s="5" t="inlineStr"/>
+      <c r="Q133" s="5" t="inlineStr"/>
+      <c r="R133" s="5" t="inlineStr"/>
+      <c r="S133" s="4" t="inlineStr">
         <is>
           <t>www.sanmarinocollege.cl</t>
         </is>
       </c>
-      <c r="Q133" s="5" t="inlineStr">
+      <c r="T133" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional  San Marino</t>
         </is>
       </c>
-      <c r="R133" s="4" t="n">
+      <c r="U133" s="4" t="n">
         <v>-29.970921</v>
       </c>
-      <c r="S133" s="4" t="n">
+      <c r="V133" s="4" t="n">
         <v>-71.29972100000001</v>
       </c>
-      <c r="T133" s="5" t="inlineStr">
+      <c r="W133" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U133" s="5" t="inlineStr">
+      <c r="X133" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V133" s="5" t="inlineStr"/>
+      <c r="Y133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -13005,29 +13866,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P134" s="7" t="inlineStr">
+      <c r="P134" s="8" t="inlineStr"/>
+      <c r="Q134" s="8" t="inlineStr"/>
+      <c r="R134" s="8" t="inlineStr"/>
+      <c r="S134" s="7" t="inlineStr">
         <is>
           <t>www.kidstropolis.cl</t>
         </is>
       </c>
-      <c r="Q134" s="8" t="inlineStr">
+      <c r="T134" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Dimar</t>
         </is>
       </c>
-      <c r="R134" s="7" t="n">
+      <c r="U134" s="7" t="n">
         <v>-29.991462</v>
       </c>
-      <c r="S134" s="7" t="n">
+      <c r="V134" s="7" t="n">
         <v>-71.318708</v>
       </c>
-      <c r="T134" s="8" t="inlineStr">
+      <c r="W134" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U134" s="8" t="inlineStr"/>
-      <c r="V134" s="8" t="inlineStr"/>
+      <c r="X134" s="8" t="inlineStr"/>
+      <c r="Y134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -13079,12 +13943,12 @@
           <t>Abtao Sector El Llano 259</t>
         </is>
       </c>
-      <c r="L135" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M135" s="13" t="inlineStr">
+      <c r="L135" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M135" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -13099,25 +13963,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P135" s="4" t="inlineStr"/>
-      <c r="Q135" s="5" t="inlineStr">
+      <c r="P135" s="5" t="inlineStr"/>
+      <c r="Q135" s="5" t="inlineStr"/>
+      <c r="R135" s="5" t="inlineStr"/>
+      <c r="S135" s="4" t="inlineStr"/>
+      <c r="T135" s="5" t="inlineStr">
         <is>
           <t>Escuela De Lenguaje Mi Mundo De Letras E.i.e.</t>
         </is>
       </c>
-      <c r="R135" s="4" t="n">
+      <c r="U135" s="4" t="n">
         <v>-29.962576</v>
       </c>
-      <c r="S135" s="4" t="n">
+      <c r="V135" s="4" t="n">
         <v>-71.33997599999999</v>
       </c>
-      <c r="T135" s="5" t="inlineStr">
+      <c r="W135" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U135" s="5" t="inlineStr"/>
-      <c r="V135" s="5" t="inlineStr"/>
+      <c r="X135" s="5" t="inlineStr"/>
+      <c r="Y135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
@@ -13189,25 +14056,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P136" s="7" t="inlineStr"/>
-      <c r="Q136" s="8" t="inlineStr">
+      <c r="P136" s="8" t="inlineStr"/>
+      <c r="Q136" s="8" t="inlineStr"/>
+      <c r="R136" s="8" t="inlineStr"/>
+      <c r="S136" s="7" t="inlineStr"/>
+      <c r="T136" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Valle Luna</t>
         </is>
       </c>
-      <c r="R136" s="7" t="n">
+      <c r="U136" s="7" t="n">
         <v>-29.98256</v>
       </c>
-      <c r="S136" s="7" t="n">
+      <c r="V136" s="7" t="n">
         <v>-71.25187</v>
       </c>
-      <c r="T136" s="8" t="inlineStr">
+      <c r="W136" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U136" s="8" t="inlineStr"/>
-      <c r="V136" s="8" t="inlineStr">
+      <c r="X136" s="8" t="inlineStr"/>
+      <c r="Y136" s="8" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -13263,12 +14133,12 @@
           <t>Pedro Aguirre Cerda Nº 613 Tierras Blancas 613</t>
         </is>
       </c>
-      <c r="L137" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M137" s="13" t="inlineStr">
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -13278,30 +14148,33 @@
           <t>Resolución exenta 1697 de fecha 10/05/2018</t>
         </is>
       </c>
-      <c r="O137" s="12" t="inlineStr">
+      <c r="O137" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P137" s="4" t="inlineStr"/>
-      <c r="Q137" s="5" t="inlineStr">
+      <c r="P137" s="5" t="inlineStr"/>
+      <c r="Q137" s="5" t="inlineStr"/>
+      <c r="R137" s="5" t="inlineStr"/>
+      <c r="S137" s="4" t="inlineStr"/>
+      <c r="T137" s="5" t="inlineStr">
         <is>
           <t>Instituto De Educación Para El Adulto E.i.e.</t>
         </is>
       </c>
-      <c r="R137" s="4" t="n">
+      <c r="U137" s="4" t="n">
         <v>-29.962376</v>
       </c>
-      <c r="S137" s="4" t="n">
+      <c r="V137" s="4" t="n">
         <v>-71.26052</v>
       </c>
-      <c r="T137" s="5" t="inlineStr">
+      <c r="W137" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U137" s="5" t="inlineStr"/>
-      <c r="V137" s="5" t="inlineStr"/>
+      <c r="X137" s="5" t="inlineStr"/>
+      <c r="Y137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -13373,33 +14246,36 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P138" s="7" t="inlineStr">
+      <c r="P138" s="8" t="inlineStr"/>
+      <c r="Q138" s="8" t="inlineStr"/>
+      <c r="R138" s="8" t="inlineStr"/>
+      <c r="S138" s="7" t="inlineStr">
         <is>
           <t>www.estrellitadebelen.com</t>
         </is>
       </c>
-      <c r="Q138" s="8" t="inlineStr">
+      <c r="T138" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Grandon Pinares</t>
         </is>
       </c>
-      <c r="R138" s="7" t="n">
+      <c r="U138" s="7" t="n">
         <v>-29.98452568</v>
       </c>
-      <c r="S138" s="7" t="n">
+      <c r="V138" s="7" t="n">
         <v>-71.33649445</v>
       </c>
-      <c r="T138" s="8" t="inlineStr">
+      <c r="W138" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U138" s="8" t="inlineStr">
+      <c r="X138" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V138" s="8" t="inlineStr"/>
+      <c r="Y138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -13451,12 +14327,12 @@
           <t>Santiago 821</t>
         </is>
       </c>
-      <c r="L139" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M139" s="13" t="inlineStr">
+      <c r="L139" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -13471,25 +14347,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P139" s="4" t="inlineStr"/>
-      <c r="Q139" s="5" t="inlineStr">
+      <c r="P139" s="5" t="inlineStr"/>
+      <c r="Q139" s="5" t="inlineStr"/>
+      <c r="R139" s="5" t="inlineStr"/>
+      <c r="S139" s="4" t="inlineStr"/>
+      <c r="T139" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Melodía</t>
         </is>
       </c>
-      <c r="R139" s="4" t="n">
+      <c r="U139" s="4" t="n">
         <v>-29.95957565</v>
       </c>
-      <c r="S139" s="4" t="n">
+      <c r="V139" s="4" t="n">
         <v>-71.25722503999999</v>
       </c>
-      <c r="T139" s="5" t="inlineStr">
+      <c r="W139" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U139" s="5" t="inlineStr"/>
-      <c r="V139" s="5" t="inlineStr"/>
+      <c r="X139" s="5" t="inlineStr"/>
+      <c r="Y139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
@@ -13561,29 +14440,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P140" s="7" t="inlineStr"/>
-      <c r="Q140" s="8" t="inlineStr">
+      <c r="P140" s="8" t="inlineStr"/>
+      <c r="Q140" s="8" t="inlineStr"/>
+      <c r="R140" s="8" t="inlineStr"/>
+      <c r="S140" s="7" t="inlineStr"/>
+      <c r="T140" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional  Jardin Infantil Mi Pequeño Genio</t>
         </is>
       </c>
-      <c r="R140" s="7" t="n">
+      <c r="U140" s="7" t="n">
         <v>-29.97445869</v>
       </c>
-      <c r="S140" s="7" t="n">
+      <c r="V140" s="7" t="n">
         <v>-71.26027679000001</v>
       </c>
-      <c r="T140" s="8" t="inlineStr">
+      <c r="W140" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U140" s="8" t="inlineStr">
+      <c r="X140" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V140" s="8" t="inlineStr"/>
+      <c r="Y140" s="8" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -13655,29 +14537,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P141" s="4" t="inlineStr"/>
-      <c r="Q141" s="5" t="inlineStr">
+      <c r="P141" s="5" t="inlineStr"/>
+      <c r="Q141" s="5" t="inlineStr"/>
+      <c r="R141" s="5" t="inlineStr"/>
+      <c r="S141" s="4" t="inlineStr"/>
+      <c r="T141" s="5" t="inlineStr">
         <is>
           <t>Mis Pequeños Angelitos Eie</t>
         </is>
       </c>
-      <c r="R141" s="4" t="n">
+      <c r="U141" s="4" t="n">
         <v>-29.97537994</v>
       </c>
-      <c r="S141" s="4" t="n">
+      <c r="V141" s="4" t="n">
         <v>-71.32496643</v>
       </c>
-      <c r="T141" s="5" t="inlineStr">
+      <c r="W141" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U141" s="5" t="inlineStr">
+      <c r="X141" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V141" s="5" t="inlineStr">
+      <c r="Y141" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -13753,25 +14638,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P142" s="7" t="inlineStr"/>
-      <c r="Q142" s="8" t="inlineStr">
+      <c r="P142" s="8" t="inlineStr"/>
+      <c r="Q142" s="8" t="inlineStr"/>
+      <c r="R142" s="8" t="inlineStr"/>
+      <c r="S142" s="7" t="inlineStr"/>
+      <c r="T142" s="8" t="inlineStr">
         <is>
           <t>Corporación Educacional Valdes Y Araya</t>
         </is>
       </c>
-      <c r="R142" s="7" t="n">
+      <c r="U142" s="7" t="n">
         <v>-29.96411514</v>
       </c>
-      <c r="S142" s="7" t="n">
+      <c r="V142" s="7" t="n">
         <v>-71.25543976</v>
       </c>
-      <c r="T142" s="8" t="inlineStr">
+      <c r="W142" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U142" s="8" t="inlineStr"/>
-      <c r="V142" s="8" t="inlineStr"/>
+      <c r="X142" s="8" t="inlineStr"/>
+      <c r="Y142" s="8" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -13823,12 +14711,12 @@
           <t>Avda. Rene Schneider , El Bosque San 1476</t>
         </is>
       </c>
-      <c r="L143" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M143" s="13" t="inlineStr">
+      <c r="L143" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -13843,25 +14731,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P143" s="4" t="inlineStr"/>
-      <c r="Q143" s="5" t="inlineStr">
+      <c r="P143" s="5" t="inlineStr"/>
+      <c r="Q143" s="5" t="inlineStr"/>
+      <c r="R143" s="5" t="inlineStr"/>
+      <c r="S143" s="4" t="inlineStr"/>
+      <c r="T143" s="5" t="inlineStr">
         <is>
           <t>Entidad Individual Educacional  El Bosque</t>
         </is>
       </c>
-      <c r="R143" s="4" t="n">
+      <c r="U143" s="4" t="n">
         <v>-29.97089958</v>
       </c>
-      <c r="S143" s="4" t="n">
+      <c r="V143" s="4" t="n">
         <v>-71.25697327</v>
       </c>
-      <c r="T143" s="5" t="inlineStr">
+      <c r="W143" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U143" s="5" t="inlineStr"/>
-      <c r="V143" s="5" t="inlineStr"/>
+      <c r="X143" s="5" t="inlineStr"/>
+      <c r="Y143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -13933,25 +14824,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P144" s="7" t="inlineStr"/>
-      <c r="Q144" s="8" t="inlineStr">
+      <c r="P144" s="8" t="inlineStr"/>
+      <c r="Q144" s="8" t="inlineStr"/>
+      <c r="R144" s="8" t="inlineStr"/>
+      <c r="S144" s="7" t="inlineStr"/>
+      <c r="T144" s="8" t="inlineStr">
         <is>
           <t>Educación Infantil Isabel Carvajal Eie</t>
         </is>
       </c>
-      <c r="R144" s="7" t="n">
+      <c r="U144" s="7" t="n">
         <v>-29.9716568</v>
       </c>
-      <c r="S144" s="7" t="n">
+      <c r="V144" s="7" t="n">
         <v>-71.25933838</v>
       </c>
-      <c r="T144" s="8" t="inlineStr">
+      <c r="W144" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U144" s="8" t="inlineStr"/>
-      <c r="V144" s="8" t="inlineStr">
+      <c r="X144" s="8" t="inlineStr"/>
+      <c r="Y144" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -14007,7 +14901,7 @@
           <t>Ignacio Carrera Pinto El Llano 955</t>
         </is>
       </c>
-      <c r="L145" s="14" t="inlineStr">
+      <c r="L145" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -14022,38 +14916,41 @@
           <t>Resolución exenta 1797 de fecha 29/06/2018</t>
         </is>
       </c>
-      <c r="O145" s="12" t="inlineStr">
+      <c r="O145" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P145" s="4" t="inlineStr">
+      <c r="P145" s="5" t="inlineStr"/>
+      <c r="Q145" s="5" t="inlineStr"/>
+      <c r="R145" s="5" t="inlineStr"/>
+      <c r="S145" s="4" t="inlineStr">
         <is>
           <t>www.kidsworldschool.cl</t>
         </is>
       </c>
-      <c r="Q145" s="5" t="inlineStr">
+      <c r="T145" s="5" t="inlineStr">
         <is>
           <t>Corporacion Educacional Kid´s World</t>
         </is>
       </c>
-      <c r="R145" s="4" t="n">
+      <c r="U145" s="4" t="n">
         <v>-29.964211</v>
       </c>
-      <c r="S145" s="4" t="n">
+      <c r="V145" s="4" t="n">
         <v>-71.342949</v>
       </c>
-      <c r="T145" s="5" t="inlineStr">
+      <c r="W145" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U145" s="5" t="inlineStr">
+      <c r="X145" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V145" s="5" t="inlineStr"/>
+      <c r="Y145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -14120,38 +15017,41 @@
           <t>Resolución exenta 2552 de fecha 13/12/2017</t>
         </is>
       </c>
-      <c r="O146" s="12" t="inlineStr">
+      <c r="O146" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P146" s="7" t="inlineStr">
+      <c r="P146" s="8" t="inlineStr"/>
+      <c r="Q146" s="8" t="inlineStr"/>
+      <c r="R146" s="8" t="inlineStr"/>
+      <c r="S146" s="7" t="inlineStr">
         <is>
           <t>www.colmigueldecervantes.cl</t>
         </is>
       </c>
-      <c r="Q146" s="8" t="inlineStr">
+      <c r="T146" s="8" t="inlineStr">
         <is>
           <t>Corporación Colegio Miguel De Cervantes De Coquimbo</t>
         </is>
       </c>
-      <c r="R146" s="7" t="n">
+      <c r="U146" s="7" t="n">
         <v>-29.96208</v>
       </c>
-      <c r="S146" s="7" t="n">
+      <c r="V146" s="7" t="n">
         <v>-71.24764999999999</v>
       </c>
-      <c r="T146" s="8" t="inlineStr">
+      <c r="W146" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U146" s="8" t="inlineStr">
+      <c r="X146" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V146" s="8" t="inlineStr"/>
+      <c r="Y146" s="8" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -14203,7 +15103,7 @@
           <t>Ñuble Nº 565, Lote Nº 10, Manzana 78, Tierras Blanca, Urbano, Coquimbo 565</t>
         </is>
       </c>
-      <c r="L147" s="14" t="inlineStr">
+      <c r="L147" s="13" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -14223,29 +15123,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P147" s="4" t="inlineStr"/>
-      <c r="Q147" s="5" t="inlineStr">
+      <c r="P147" s="5" t="inlineStr"/>
+      <c r="Q147" s="5" t="inlineStr"/>
+      <c r="R147" s="5" t="inlineStr"/>
+      <c r="S147" s="4" t="inlineStr"/>
+      <c r="T147" s="5" t="inlineStr">
         <is>
           <t>Corporación Educacional Rayün De Coquimbo</t>
         </is>
       </c>
-      <c r="R147" s="4" t="n">
+      <c r="U147" s="4" t="n">
         <v>-29.962688</v>
       </c>
-      <c r="S147" s="4" t="n">
+      <c r="V147" s="4" t="n">
         <v>-71.261011</v>
       </c>
-      <c r="T147" s="5" t="inlineStr">
+      <c r="W147" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U147" s="5" t="inlineStr">
+      <c r="X147" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V147" s="5" t="inlineStr">
+      <c r="Y147" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -14316,34 +15219,37 @@
           <t>Resolución exenta 2273 de fecha 25/10/2016</t>
         </is>
       </c>
-      <c r="O148" s="12" t="inlineStr">
+      <c r="O148" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P148" s="7" t="inlineStr">
+      <c r="P148" s="8" t="inlineStr"/>
+      <c r="Q148" s="8" t="inlineStr"/>
+      <c r="R148" s="8" t="inlineStr"/>
+      <c r="S148" s="7" t="inlineStr">
         <is>
           <t>www.amazinggraceco.cl</t>
         </is>
       </c>
-      <c r="Q148" s="8" t="inlineStr">
+      <c r="T148" s="8" t="inlineStr">
         <is>
           <t>Sociedad Educacional Shalom  Spa</t>
         </is>
       </c>
-      <c r="R148" s="7" t="n">
+      <c r="U148" s="7" t="n">
         <v>-29.96907</v>
       </c>
-      <c r="S148" s="7" t="n">
+      <c r="V148" s="7" t="n">
         <v>-71.29998000000001</v>
       </c>
-      <c r="T148" s="8" t="inlineStr">
+      <c r="W148" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U148" s="8" t="inlineStr"/>
-      <c r="V148" s="8" t="inlineStr"/>
+      <c r="X148" s="8" t="inlineStr"/>
+      <c r="Y148" s="8" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -14395,12 +15301,12 @@
           <t>Las Azucenas Nº 690, Sindempart, Sector Urbano, De La Comuna De Coquimbo 690</t>
         </is>
       </c>
-      <c r="L149" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M149" s="13" t="inlineStr">
+      <c r="L149" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M149" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -14410,34 +15316,37 @@
           <t>Resolución exenta 2856 de fecha 14/11/2018</t>
         </is>
       </c>
-      <c r="O149" s="12" t="inlineStr">
+      <c r="O149" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P149" s="4" t="inlineStr">
+      <c r="P149" s="5" t="inlineStr"/>
+      <c r="Q149" s="5" t="inlineStr"/>
+      <c r="R149" s="5" t="inlineStr"/>
+      <c r="S149" s="4" t="inlineStr">
         <is>
           <t>www.colegioconquistadores.cl</t>
         </is>
       </c>
-      <c r="Q149" s="5" t="inlineStr">
+      <c r="T149" s="5" t="inlineStr">
         <is>
           <t>Arturo Javier Galleguillos Trigo Argat E.i.r.</t>
         </is>
       </c>
-      <c r="R149" s="4" t="n">
+      <c r="U149" s="4" t="n">
         <v>-29.983309</v>
       </c>
-      <c r="S149" s="4" t="n">
+      <c r="V149" s="4" t="n">
         <v>-71.34519400000001</v>
       </c>
-      <c r="T149" s="5" t="inlineStr">
+      <c r="W149" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U149" s="5" t="inlineStr"/>
-      <c r="V149" s="5" t="inlineStr"/>
+      <c r="X149" s="5" t="inlineStr"/>
+      <c r="Y149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -14504,34 +15413,37 @@
           <t>Resolución exenta 1147 de fecha 16/04/1992</t>
         </is>
       </c>
-      <c r="O150" s="12" t="inlineStr">
+      <c r="O150" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P150" s="7" t="inlineStr"/>
-      <c r="Q150" s="8" t="inlineStr">
+      <c r="P150" s="8" t="inlineStr"/>
+      <c r="Q150" s="8" t="inlineStr"/>
+      <c r="R150" s="8" t="inlineStr"/>
+      <c r="S150" s="7" t="inlineStr"/>
+      <c r="T150" s="8" t="inlineStr">
         <is>
           <t>Saint Mary School S.a.</t>
         </is>
       </c>
-      <c r="R150" s="7" t="n">
+      <c r="U150" s="7" t="n">
         <v>-29.98781012</v>
       </c>
-      <c r="S150" s="7" t="n">
+      <c r="V150" s="7" t="n">
         <v>-71.34183347</v>
       </c>
-      <c r="T150" s="8" t="inlineStr">
+      <c r="W150" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U150" s="8" t="inlineStr">
+      <c r="X150" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V150" s="8" t="inlineStr">
+      <c r="Y150" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -14602,38 +15514,41 @@
           <t>Resolución exenta 0005 de fecha 06/01/2015</t>
         </is>
       </c>
-      <c r="O151" s="12" t="inlineStr">
+      <c r="O151" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P151" s="4" t="inlineStr">
+      <c r="P151" s="5" t="inlineStr"/>
+      <c r="Q151" s="5" t="inlineStr"/>
+      <c r="R151" s="5" t="inlineStr"/>
+      <c r="S151" s="4" t="inlineStr">
         <is>
           <t>www.cassjps.cl</t>
         </is>
       </c>
-      <c r="Q151" s="5" t="inlineStr">
+      <c r="T151" s="5" t="inlineStr">
         <is>
           <t>Jorge Lorenzo Ramirez Flores Educacion De Adultos Eirl</t>
         </is>
       </c>
-      <c r="R151" s="4" t="n">
+      <c r="U151" s="4" t="n">
         <v>-29.96345211</v>
       </c>
-      <c r="S151" s="4" t="n">
+      <c r="V151" s="4" t="n">
         <v>-71.26163805</v>
       </c>
-      <c r="T151" s="5" t="inlineStr">
+      <c r="W151" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U151" s="5" t="inlineStr">
+      <c r="X151" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V151" s="5" t="inlineStr">
+      <c r="Y151" s="5" t="inlineStr">
         <is>
           <t>Número con formato irregular: verificar; Mismo colegio con dos RBD (sedes)</t>
         </is>
@@ -14705,33 +15620,36 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P152" s="7" t="inlineStr">
+      <c r="P152" s="8" t="inlineStr"/>
+      <c r="Q152" s="8" t="inlineStr"/>
+      <c r="R152" s="8" t="inlineStr"/>
+      <c r="S152" s="7" t="inlineStr">
         <is>
           <t>www.cassjps.cl</t>
         </is>
       </c>
-      <c r="Q152" s="8" t="inlineStr">
+      <c r="T152" s="8" t="inlineStr">
         <is>
           <t>Jorge Lorenzo Ramirez Flores Educacion De Adultos Eirl</t>
         </is>
       </c>
-      <c r="R152" s="7" t="n">
+      <c r="U152" s="7" t="n">
         <v>-29.963522</v>
       </c>
-      <c r="S152" s="7" t="n">
+      <c r="V152" s="7" t="n">
         <v>-71.261686</v>
       </c>
-      <c r="T152" s="8" t="inlineStr">
+      <c r="W152" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U152" s="8" t="inlineStr">
+      <c r="X152" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V152" s="8" t="inlineStr">
+      <c r="Y152" s="8" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar; Sin matrícula informada en 2025; Mismo colegio con dos RBD (sedes)</t>
         </is>
@@ -14802,38 +15720,41 @@
           <t>Resolución exenta 613 de fecha 26/03/2018</t>
         </is>
       </c>
-      <c r="O153" s="12" t="inlineStr">
+      <c r="O153" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P153" s="4" t="inlineStr">
+      <c r="P153" s="5" t="inlineStr"/>
+      <c r="Q153" s="5" t="inlineStr"/>
+      <c r="R153" s="5" t="inlineStr"/>
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>www.colegiodelalbacoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q153" s="5" t="inlineStr">
+      <c r="T153" s="5" t="inlineStr">
         <is>
           <t>Sociedad Educacional Del Alba S.a.</t>
         </is>
       </c>
-      <c r="R153" s="4" t="n">
+      <c r="U153" s="4" t="n">
         <v>-29.95225595</v>
       </c>
-      <c r="S153" s="4" t="n">
+      <c r="V153" s="4" t="n">
         <v>-71.26876285</v>
       </c>
-      <c r="T153" s="5" t="inlineStr">
+      <c r="W153" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U153" s="5" t="inlineStr">
+      <c r="X153" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V153" s="5" t="inlineStr"/>
+      <c r="Y153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
@@ -14900,38 +15821,41 @@
           <t>Resolución exenta 505 de fecha 14/06/1985</t>
         </is>
       </c>
-      <c r="O154" s="12" t="inlineStr">
+      <c r="O154" s="14" t="inlineStr">
         <is>
           <t>Por completar</t>
         </is>
       </c>
-      <c r="P154" s="7" t="inlineStr">
+      <c r="P154" s="8" t="inlineStr"/>
+      <c r="Q154" s="8" t="inlineStr"/>
+      <c r="R154" s="8" t="inlineStr"/>
+      <c r="S154" s="7" t="inlineStr">
         <is>
           <t>www.colegioparticularloscarrera.cl</t>
         </is>
       </c>
-      <c r="Q154" s="8" t="inlineStr">
+      <c r="T154" s="8" t="inlineStr">
         <is>
           <t>Manuel A. Santander Escobar Serv.ed. E.i.r.l.</t>
         </is>
       </c>
-      <c r="R154" s="7" t="n">
+      <c r="U154" s="7" t="n">
         <v>-29.96313267</v>
       </c>
-      <c r="S154" s="7" t="n">
+      <c r="V154" s="7" t="n">
         <v>-71.33971086</v>
       </c>
-      <c r="T154" s="8" t="inlineStr">
+      <c r="W154" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U154" s="8" t="inlineStr">
+      <c r="X154" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V154" s="8" t="inlineStr"/>
+      <c r="Y154" s="8" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -14959,7 +15883,7 @@
       <c r="G155" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H155" s="13" t="inlineStr">
+      <c r="H155" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -14979,12 +15903,12 @@
           <t>Avenida Amanecer 1621</t>
         </is>
       </c>
-      <c r="L155" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M155" s="13" t="inlineStr">
+      <c r="L155" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M155" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -14999,25 +15923,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P155" s="4" t="inlineStr"/>
-      <c r="Q155" s="5" t="inlineStr">
+      <c r="P155" s="5" t="inlineStr"/>
+      <c r="Q155" s="5" t="inlineStr"/>
+      <c r="R155" s="5" t="inlineStr"/>
+      <c r="S155" s="4" t="inlineStr"/>
+      <c r="T155" s="5" t="inlineStr">
         <is>
           <t>Sociedad Educacional Vive Sa</t>
         </is>
       </c>
-      <c r="R155" s="4" t="n">
+      <c r="U155" s="4" t="n">
         <v>-29.9665589</v>
       </c>
-      <c r="S155" s="4" t="n">
+      <c r="V155" s="4" t="n">
         <v>-71.2918622</v>
       </c>
-      <c r="T155" s="5" t="inlineStr">
+      <c r="W155" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U155" s="5" t="inlineStr"/>
-      <c r="V155" s="5" t="inlineStr">
+      <c r="X155" s="5" t="inlineStr"/>
+      <c r="Y155" s="5" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -15089,29 +16016,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P156" s="7" t="inlineStr">
+      <c r="P156" s="8" t="inlineStr"/>
+      <c r="Q156" s="8" t="inlineStr"/>
+      <c r="R156" s="8" t="inlineStr"/>
+      <c r="S156" s="7" t="inlineStr">
         <is>
           <t>www.arcoiriscoquimbo.cl</t>
         </is>
       </c>
-      <c r="Q156" s="8" t="inlineStr">
+      <c r="T156" s="8" t="inlineStr">
         <is>
           <t>Arcoiris Servicios Educacionales Eirl</t>
         </is>
       </c>
-      <c r="R156" s="7" t="n">
+      <c r="U156" s="7" t="n">
         <v>-29.988585</v>
       </c>
-      <c r="S156" s="7" t="n">
+      <c r="V156" s="7" t="n">
         <v>-71.33779</v>
       </c>
-      <c r="T156" s="8" t="inlineStr">
+      <c r="W156" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U156" s="8" t="inlineStr"/>
-      <c r="V156" s="8" t="inlineStr">
+      <c r="X156" s="8" t="inlineStr"/>
+      <c r="Y156" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar; Sin matrícula informada en 2025</t>
         </is>
@@ -15143,7 +16073,7 @@
       <c r="G157" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H157" s="13" t="inlineStr">
+      <c r="H157" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15163,12 +16093,12 @@
           <t>Avda Ossandon 150 El Llano</t>
         </is>
       </c>
-      <c r="L157" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M157" s="13" t="inlineStr">
+      <c r="L157" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M157" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15183,25 +16113,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P157" s="4" t="inlineStr"/>
-      <c r="Q157" s="5" t="inlineStr">
+      <c r="P157" s="5" t="inlineStr"/>
+      <c r="Q157" s="5" t="inlineStr"/>
+      <c r="R157" s="5" t="inlineStr"/>
+      <c r="S157" s="4" t="inlineStr"/>
+      <c r="T157" s="5" t="inlineStr">
         <is>
           <t>Carmen Julia Muñoz Ramos Eirl</t>
         </is>
       </c>
-      <c r="R157" s="4" t="n">
+      <c r="U157" s="4" t="n">
         <v>-29.95997399</v>
       </c>
-      <c r="S157" s="4" t="n">
+      <c r="V157" s="4" t="n">
         <v>-71.34087038</v>
       </c>
-      <c r="T157" s="5" t="inlineStr">
+      <c r="W157" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U157" s="5" t="inlineStr"/>
-      <c r="V157" s="5" t="inlineStr">
+      <c r="X157" s="5" t="inlineStr"/>
+      <c r="Y157" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar; Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -15277,29 +16210,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P158" s="7" t="inlineStr"/>
-      <c r="Q158" s="8" t="inlineStr">
+      <c r="P158" s="8" t="inlineStr"/>
+      <c r="Q158" s="8" t="inlineStr"/>
+      <c r="R158" s="8" t="inlineStr"/>
+      <c r="S158" s="7" t="inlineStr"/>
+      <c r="T158" s="8" t="inlineStr">
         <is>
           <t>Sala Cuna Y Jardin Infantil Alejandra Diaz Bo</t>
         </is>
       </c>
-      <c r="R158" s="7" t="n">
+      <c r="U158" s="7" t="n">
         <v>-29.983498</v>
       </c>
-      <c r="S158" s="7" t="n">
+      <c r="V158" s="7" t="n">
         <v>-71.337204</v>
       </c>
-      <c r="T158" s="8" t="inlineStr">
+      <c r="W158" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U158" s="8" t="inlineStr">
+      <c r="X158" s="8" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V158" s="8" t="inlineStr"/>
+      <c r="Y158" s="8" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -15371,29 +16307,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P159" s="4" t="inlineStr"/>
-      <c r="Q159" s="5" t="inlineStr">
+      <c r="P159" s="5" t="inlineStr"/>
+      <c r="Q159" s="5" t="inlineStr"/>
+      <c r="R159" s="5" t="inlineStr"/>
+      <c r="S159" s="4" t="inlineStr"/>
+      <c r="T159" s="5" t="inlineStr">
         <is>
           <t>Maria Olivia Carrillo Moreno</t>
         </is>
       </c>
-      <c r="R159" s="4" t="n">
+      <c r="U159" s="4" t="n">
         <v>-29.984518</v>
       </c>
-      <c r="S159" s="4" t="n">
+      <c r="V159" s="4" t="n">
         <v>-71.36190000000001</v>
       </c>
-      <c r="T159" s="5" t="inlineStr">
+      <c r="W159" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U159" s="5" t="inlineStr">
+      <c r="X159" s="5" t="inlineStr">
         <is>
           <t>PEI del establecimiento (MINEDUC)</t>
         </is>
       </c>
-      <c r="V159" s="5" t="inlineStr">
+      <c r="Y159" s="5" t="inlineStr">
         <is>
           <t>Celular antiguo de 8 dígitos, se antepuso 9: verificar</t>
         </is>
@@ -15469,25 +16408,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P160" s="7" t="inlineStr"/>
-      <c r="Q160" s="8" t="inlineStr">
+      <c r="P160" s="8" t="inlineStr"/>
+      <c r="Q160" s="8" t="inlineStr"/>
+      <c r="R160" s="8" t="inlineStr"/>
+      <c r="S160" s="7" t="inlineStr"/>
+      <c r="T160" s="8" t="inlineStr">
         <is>
           <t>Arturo Javier Galleguillos Trigo Argat E.i.r.</t>
         </is>
       </c>
-      <c r="R160" s="7" t="n">
+      <c r="U160" s="7" t="n">
         <v>-29.98281</v>
       </c>
-      <c r="S160" s="7" t="n">
+      <c r="V160" s="7" t="n">
         <v>-71.34533</v>
       </c>
-      <c r="T160" s="8" t="inlineStr">
+      <c r="W160" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U160" s="8" t="inlineStr"/>
-      <c r="V160" s="8" t="inlineStr">
+      <c r="X160" s="8" t="inlineStr"/>
+      <c r="Y160" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar</t>
         </is>
@@ -15519,12 +16461,12 @@
       <c r="G161" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H161" s="13" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="I161" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15539,12 +16481,12 @@
           <t>Los Geranios 292 292</t>
         </is>
       </c>
-      <c r="L161" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M161" s="13" t="inlineStr">
+      <c r="L161" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M161" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15559,25 +16501,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P161" s="4" t="inlineStr"/>
-      <c r="Q161" s="5" t="inlineStr">
+      <c r="P161" s="5" t="inlineStr"/>
+      <c r="Q161" s="5" t="inlineStr"/>
+      <c r="R161" s="5" t="inlineStr"/>
+      <c r="S161" s="4" t="inlineStr"/>
+      <c r="T161" s="5" t="inlineStr">
         <is>
           <t>Servicios Educacionales Rojas Lemus Limitada</t>
         </is>
       </c>
-      <c r="R161" s="4" t="n">
+      <c r="U161" s="4" t="n">
         <v>-29.988074</v>
       </c>
-      <c r="S161" s="4" t="n">
+      <c r="V161" s="4" t="n">
         <v>-71.35036599999999</v>
       </c>
-      <c r="T161" s="5" t="inlineStr">
+      <c r="W161" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U161" s="5" t="inlineStr"/>
-      <c r="V161" s="5" t="inlineStr">
+      <c r="X161" s="5" t="inlineStr"/>
+      <c r="Y161" s="5" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -15649,29 +16594,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P162" s="7" t="inlineStr">
+      <c r="P162" s="8" t="inlineStr"/>
+      <c r="Q162" s="8" t="inlineStr"/>
+      <c r="R162" s="8" t="inlineStr"/>
+      <c r="S162" s="7" t="inlineStr">
         <is>
           <t>jardinpucara.cl</t>
         </is>
       </c>
-      <c r="Q162" s="8" t="inlineStr">
+      <c r="T162" s="8" t="inlineStr">
         <is>
           <t>Sociedad Educacional Pucara Limitada</t>
         </is>
       </c>
-      <c r="R162" s="7" t="n">
+      <c r="U162" s="7" t="n">
         <v>-29.966333</v>
       </c>
-      <c r="S162" s="7" t="n">
+      <c r="V162" s="7" t="n">
         <v>-71.2475</v>
       </c>
-      <c r="T162" s="8" t="inlineStr">
+      <c r="W162" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U162" s="8" t="inlineStr"/>
-      <c r="V162" s="8" t="inlineStr">
+      <c r="X162" s="8" t="inlineStr"/>
+      <c r="Y162" s="8" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025</t>
         </is>
@@ -15723,12 +16671,12 @@
           <t>Av El Sauce 909, Sindempart</t>
         </is>
       </c>
-      <c r="L163" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M163" s="13" t="inlineStr">
+      <c r="L163" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M163" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15743,29 +16691,32 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P163" s="4" t="inlineStr">
+      <c r="P163" s="5" t="inlineStr"/>
+      <c r="Q163" s="5" t="inlineStr"/>
+      <c r="R163" s="5" t="inlineStr"/>
+      <c r="S163" s="4" t="inlineStr">
         <is>
           <t>www.santaanna.cl</t>
         </is>
       </c>
-      <c r="Q163" s="5" t="inlineStr">
+      <c r="T163" s="5" t="inlineStr">
         <is>
           <t>Educacion Infantil Santa Anna S.a.c.</t>
         </is>
       </c>
-      <c r="R163" s="4" t="n">
+      <c r="U163" s="4" t="n">
         <v>-29.986458</v>
       </c>
-      <c r="S163" s="4" t="n">
+      <c r="V163" s="4" t="n">
         <v>-71.34229999999999</v>
       </c>
-      <c r="T163" s="5" t="inlineStr">
+      <c r="W163" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U163" s="5" t="inlineStr"/>
-      <c r="V163" s="5" t="inlineStr">
+      <c r="X163" s="5" t="inlineStr"/>
+      <c r="Y163" s="5" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar; Sin matrícula informada en 2025</t>
         </is>
@@ -15837,25 +16788,28 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P164" s="7" t="inlineStr"/>
-      <c r="Q164" s="8" t="inlineStr">
+      <c r="P164" s="8" t="inlineStr"/>
+      <c r="Q164" s="8" t="inlineStr"/>
+      <c r="R164" s="8" t="inlineStr"/>
+      <c r="S164" s="7" t="inlineStr"/>
+      <c r="T164" s="8" t="inlineStr">
         <is>
           <t>Servicio De Salud Coquimbo Iv Region</t>
         </is>
       </c>
-      <c r="R164" s="7" t="n">
+      <c r="U164" s="7" t="n">
         <v>-29.968548</v>
       </c>
-      <c r="S164" s="7" t="n">
+      <c r="V164" s="7" t="n">
         <v>-71.33642</v>
       </c>
-      <c r="T164" s="8" t="inlineStr">
+      <c r="W164" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U164" s="8" t="inlineStr"/>
-      <c r="V164" s="8" t="inlineStr">
+      <c r="X164" s="8" t="inlineStr"/>
+      <c r="Y164" s="8" t="inlineStr">
         <is>
           <t>Número antiguo de 6 dígitos, se antepuso 2: verificar; Sin matrícula informada en 2025</t>
         </is>
@@ -15887,7 +16841,7 @@
       <c r="G165" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H165" s="13" t="inlineStr">
+      <c r="H165" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15907,12 +16861,12 @@
           <t>Lincoyan 218</t>
         </is>
       </c>
-      <c r="L165" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M165" s="13" t="inlineStr">
+      <c r="L165" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M165" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -15927,21 +16881,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P165" s="4" t="inlineStr"/>
-      <c r="Q165" s="5" t="inlineStr">
+      <c r="P165" s="5" t="inlineStr"/>
+      <c r="Q165" s="5" t="inlineStr"/>
+      <c r="R165" s="5" t="inlineStr"/>
+      <c r="S165" s="4" t="inlineStr"/>
+      <c r="T165" s="5" t="inlineStr">
         <is>
           <t>Entretenidamente Kids Limitada</t>
         </is>
       </c>
-      <c r="R165" s="4" t="n"/>
-      <c r="S165" s="4" t="n"/>
-      <c r="T165" s="5" t="inlineStr">
+      <c r="U165" s="4" t="n"/>
+      <c r="V165" s="4" t="n"/>
+      <c r="W165" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U165" s="5" t="inlineStr"/>
-      <c r="V165" s="5" t="inlineStr">
+      <c r="X165" s="5" t="inlineStr"/>
+      <c r="Y165" s="5" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -16013,21 +16970,24 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P166" s="7" t="inlineStr"/>
-      <c r="Q166" s="8" t="inlineStr">
+      <c r="P166" s="8" t="inlineStr"/>
+      <c r="Q166" s="8" t="inlineStr"/>
+      <c r="R166" s="8" t="inlineStr"/>
+      <c r="S166" s="7" t="inlineStr"/>
+      <c r="T166" s="8" t="inlineStr">
         <is>
           <t>Sociedad Educacional Aliwen Ltda</t>
         </is>
       </c>
-      <c r="R166" s="7" t="n"/>
-      <c r="S166" s="7" t="n"/>
-      <c r="T166" s="8" t="inlineStr">
+      <c r="U166" s="7" t="n"/>
+      <c r="V166" s="7" t="n"/>
+      <c r="W166" s="8" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U166" s="8" t="inlineStr"/>
-      <c r="V166" s="8" t="inlineStr">
+      <c r="X166" s="8" t="inlineStr"/>
+      <c r="Y166" s="8" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025; Sin director informado en MIME</t>
         </is>
@@ -16059,7 +17019,7 @@
       <c r="G167" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H167" s="13" t="inlineStr">
+      <c r="H167" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -16079,12 +17039,12 @@
           <t>Calle Almirante Allard N° 425, Lote N° 19, Sector Urbano, De La Comuna De La Serena 425</t>
         </is>
       </c>
-      <c r="L167" s="14" t="inlineStr">
-        <is>
-          <t>Sin información</t>
-        </is>
-      </c>
-      <c r="M167" s="13" t="inlineStr">
+      <c r="L167" s="13" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="M167" s="12" t="inlineStr">
         <is>
           <t>Sin información</t>
         </is>
@@ -16099,32 +17059,35 @@
           <t>No aplica</t>
         </is>
       </c>
-      <c r="P167" s="4" t="inlineStr"/>
-      <c r="Q167" s="5" t="inlineStr">
+      <c r="P167" s="5" t="inlineStr"/>
+      <c r="Q167" s="5" t="inlineStr"/>
+      <c r="R167" s="5" t="inlineStr"/>
+      <c r="S167" s="4" t="inlineStr"/>
+      <c r="T167" s="5" t="inlineStr">
         <is>
           <t>Educacional Paz Limitada</t>
         </is>
       </c>
-      <c r="R167" s="4" t="n">
+      <c r="U167" s="4" t="n">
         <v>-29.9183533</v>
       </c>
-      <c r="S167" s="4" t="n">
+      <c r="V167" s="4" t="n">
         <v>-71.25545289999999</v>
       </c>
-      <c r="T167" s="5" t="inlineStr">
+      <c r="W167" s="5" t="inlineStr">
         <is>
           <t>MINEDUC, Ficha del Establecimiento (MIME), consulta 05.10.2026</t>
         </is>
       </c>
-      <c r="U167" s="5" t="inlineStr"/>
-      <c r="V167" s="5" t="inlineStr">
+      <c r="X167" s="5" t="inlineStr"/>
+      <c r="Y167" s="5" t="inlineStr">
         <is>
           <t>Sin matrícula informada en 2025; MIME indica dirección en comuna de La Serena: verificar; Sin director informado en MIME</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V167"/>
+  <autoFilter ref="A4:Y167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -16136,7 +17099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -16145,6 +17108,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16182,6 +17146,11 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
+          <t>Presidente/a CEAL informado</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
           <t>CEAL por completar</t>
         </is>
       </c>
@@ -16209,6 +17178,10 @@
         <v/>
       </c>
       <c r="F4" s="17">
+        <f>COUNTIFS(Base!$D$5:$D$167,A4,Base!$O$5:$O$167,"Informado*")</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
         <f>COUNTIFS(Base!$D$5:$D$167,A4,Base!$O$5:$O$167,"Por completar")</f>
         <v/>
       </c>
@@ -16236,6 +17209,10 @@
         <v/>
       </c>
       <c r="F5" s="17">
+        <f>COUNTIFS(Base!$D$5:$D$167,A5,Base!$O$5:$O$167,"Informado*")</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
         <f>COUNTIFS(Base!$D$5:$D$167,A5,Base!$O$5:$O$167,"Por completar")</f>
         <v/>
       </c>
@@ -16263,6 +17240,10 @@
         <v/>
       </c>
       <c r="F6" s="17">
+        <f>COUNTIFS(Base!$D$5:$D$167,A6,Base!$O$5:$O$167,"Informado*")</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
         <f>COUNTIFS(Base!$D$5:$D$167,A6,Base!$O$5:$O$167,"Por completar")</f>
         <v/>
       </c>
@@ -16290,6 +17271,10 @@
         <v/>
       </c>
       <c r="F7" s="17">
+        <f>COUNTIFS(Base!$D$5:$D$167,A7,Base!$O$5:$O$167,"Informado*")</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
         <f>COUNTIFS(Base!$D$5:$D$167,A7,Base!$O$5:$O$167,"Por completar")</f>
         <v/>
       </c>
@@ -16318,6 +17303,10 @@
       </c>
       <c r="F8" s="19">
         <f>SUM(F4:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>SUM(G4:G7)</f>
         <v/>
       </c>
     </row>
@@ -16339,7 +17328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16452,17 +17441,29 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>No hay un registro público. Los centros de estudiantes se eligen cada año, por lo general entre marzo y mayo, y la mayoría de quienes los presiden son menores de edad. La columna queda en amarillo ("Por completar") en los 92 establecimientos con 2.° ciclo básico, media o adultos. Se sugiere pedir el dato al SLEP Puerto Cordillera y a cada establecimiento particular mediante oficio, y limitar su uso a fines de vinculación institucional (Ley 19.628, sobre protección de la vida privada).</t>
+          <t>Establecimientos públicos: se integró la nómina 2026 de presidentas y presidentes de centros de estudiantes y gobiernos estudiantiles del SLEP Puerto Cordillera (38 casos, cruzados por establecimiento con su RBD). Coincide con todos los establecimientos públicos de Coquimbo con matrícula; la Escuela de Camarones no figura porque no tuvo matrícula en 2025. Incluye dos escuelas especiales (Jean Piaget y Juan Sandoval) que antes figuraban como "No aplica". Particulares: no hay registro público y quedan 55 en amarillo ("Por completar"). Cuando el correo de la nómina es el institucional del establecimiento, se indica entre paréntesis.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
+          <t>Resguardo de datos</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>La nómina contiene nombres y correos personales de estudiantes, en su mayoría menores de edad. Usar solo para vinculación institucional, no difundir y no publicar la planilla (Ley 19.628 y Ley 21.719 sobre protección de datos personales). Para contactos formales, preferir el correo institucional del establecimiento con copia a la dirección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
           <t>Fuera del universo</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>No se incluyen los jardines JUNJI de administración directa ni los de Fundación Integra, que no tienen RBD MINEDUC. Tampoco los establecimientos del SLEP ubicados en Andacollo.</t>
         </is>

--- a/claude/05.10.2026 - BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO/BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO.xlsx
+++ b/claude/05.10.2026 - BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO/BASE ESTABLECIMIENTOS EDUCACIONALES COQUIMBO.xlsx
@@ -17441,7 +17441,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Establecimientos públicos: se integró la nómina 2026 de presidentas y presidentes de centros de estudiantes y gobiernos estudiantiles del SLEP Puerto Cordillera (38 casos, cruzados por establecimiento con su RBD). Coincide con todos los establecimientos públicos de Coquimbo con matrícula; la Escuela de Camarones no figura porque no tuvo matrícula en 2025. Incluye dos escuelas especiales (Jean Piaget y Juan Sandoval) que antes figuraban como "No aplica". Particulares: no hay registro público y quedan 55 en amarillo ("Por completar"). Cuando el correo de la nómina es el institucional del establecimiento, se indica entre paréntesis.</t>
+          <t>Establecimientos públicos: se integró la nómina 2026 de presidentas y presidentes de centros de estudiantes y gobiernos estudiantiles del SLEP Puerto Cordillera (38 casos, cruzados por establecimiento con su RBD). Coincide con todos los establecimientos públicos de Coquimbo con matrícula; la Escuela de Camarones no figura porque no tuvo matrícula en 2025. Incluye dos escuelas especiales (Jean Piaget y Juan Sandoval) que antes figuraban como "No aplica". Particulares: no hay registro público y quedan 56 en amarillo ("Por completar"). Cuando el correo de la nómina es el institucional del establecimiento, se indica entre paréntesis.</t>
         </is>
       </c>
     </row>
